--- a/inst/resources/dependency_schema_data_household_template.xlsx
+++ b/inst/resources/dependency_schema_data_household_template.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF71D149-0280-40DA-9004-7ADEC66A4EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C32BFF-039D-4127-A18E-B600D7F5AE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15135" yWindow="75" windowWidth="14250" windowHeight="15405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$250</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="758">
   <si>
     <t>rule_type</t>
   </si>
@@ -169,351 +169,9 @@
     <t>flag_warning</t>
   </si>
   <si>
-    <t>flag_first_second_priority_need</t>
-  </si>
-  <si>
-    <t>first_priority_need,second_priority_need</t>
-  </si>
-  <si>
-    <t>first_priority_need != second_priority_need</t>
-  </si>
-  <si>
-    <t>flag_first_third_priority_need</t>
-  </si>
-  <si>
-    <t>first_priority_need,third_priority_need</t>
-  </si>
-  <si>
-    <t>first_priority_need != third_priority_need</t>
-  </si>
-  <si>
-    <t>flag_second_third_priority_need</t>
-  </si>
-  <si>
-    <t>second_priority_need,third_priority_need</t>
-  </si>
-  <si>
-    <t>third_priority_need != second_priority_need</t>
-  </si>
-  <si>
-    <t>flag_first_second_none_needs</t>
-  </si>
-  <si>
-    <t>first_priority_need == 'none'</t>
-  </si>
-  <si>
-    <t>is.na(second_priority_need)</t>
-  </si>
-  <si>
-    <t>flag_first_third_none_needs</t>
-  </si>
-  <si>
-    <t>is.na(third_priority_need)</t>
-  </si>
-  <si>
-    <t>flag_second_third_none_needs</t>
-  </si>
-  <si>
-    <t>second_priority_need == 'none'</t>
-  </si>
-  <si>
-    <t>flag_second_third_needs_na</t>
-  </si>
-  <si>
-    <t>flag_first_priority_need_other_sl1</t>
-  </si>
-  <si>
-    <t>first_priority_need,first_priority_need_other</t>
-  </si>
-  <si>
-    <t>first_priority_need == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(first_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_first_priority_need_other_sl2</t>
-  </si>
-  <si>
-    <t>first_priority_need != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(first_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_second_priority_need_other_sl1</t>
-  </si>
-  <si>
-    <t>second_priority_need,second_priority_need_other</t>
-  </si>
-  <si>
-    <t>second_priority_need == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(second_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_second_priority_need_other_sl2</t>
-  </si>
-  <si>
-    <t>second_priority_need != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(second_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_third_priority_need_other_sl1</t>
-  </si>
-  <si>
-    <t>third_priority_need,third_priority_need_other</t>
-  </si>
-  <si>
-    <t>third_priority_need == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(third_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_third_priority_need_other_sl2</t>
-  </si>
-  <si>
-    <t>third_priority_need != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(third_priority_need_other)</t>
-  </si>
-  <si>
-    <t>flag_dod_not_displaced</t>
-  </si>
-  <si>
-    <t>dod_idp_returnee,residency_status</t>
-  </si>
-  <si>
-    <t>dod_idp_returnee == 'yes'</t>
-  </si>
-  <si>
-    <t>residency_status != 'host'</t>
-  </si>
-  <si>
-    <t>flag_date_dod_not_displaced</t>
-  </si>
-  <si>
-    <t>date_dod_idp_returnee,residency_status</t>
-  </si>
-  <si>
-    <t>!is.na(date_dod_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_date_dod_start</t>
-  </si>
-  <si>
-    <t>date_dod_idp_returnee,start</t>
-  </si>
-  <si>
-    <t>date_dod_idp_returnee &lt; start</t>
-  </si>
-  <si>
-    <t>flag_date_dod_end</t>
-  </si>
-  <si>
-    <t>date_dod_idp_returnee,end</t>
-  </si>
-  <si>
-    <t>date_dod_idp_returnee &lt; end</t>
-  </si>
-  <si>
-    <t>flag_date_doa_start</t>
-  </si>
-  <si>
-    <t>date_doa_idp_returnee,start</t>
-  </si>
-  <si>
-    <t>date_doa_idp_returnee &lt; start</t>
-  </si>
-  <si>
-    <t>flag_date_doa_end</t>
-  </si>
-  <si>
-    <t>date_doa_idp_returnee,end</t>
-  </si>
-  <si>
-    <t>date_doa_idp_returnee &lt; end</t>
-  </si>
-  <si>
-    <t>flag_residency_dod1</t>
-  </si>
-  <si>
-    <t>residency_status,dod_idp_returnee</t>
-  </si>
-  <si>
-    <t>residency_status == 'host'</t>
-  </si>
-  <si>
-    <t>is.na(dod_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_dod2</t>
-  </si>
-  <si>
-    <t>!is.na(dod_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_dod_date1</t>
-  </si>
-  <si>
-    <t>residency_status,date_dod_idp_returnee</t>
-  </si>
-  <si>
-    <t>is.na(date_dod_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_dod_date2</t>
-  </si>
-  <si>
-    <t>flag_residency_doa1</t>
-  </si>
-  <si>
-    <t>residency_status,doa_idp_returnee</t>
-  </si>
-  <si>
-    <t>is.na(doa_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_doa2</t>
-  </si>
-  <si>
-    <t>!is.na(doa_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_date_doa1</t>
-  </si>
-  <si>
-    <t>residency_status,date_doa_idp_returnee</t>
-  </si>
-  <si>
-    <t>is.na(date_doa_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_residency_date_doa2</t>
-  </si>
-  <si>
-    <t>!is.na(date_doa_idp_returnee)</t>
-  </si>
-  <si>
-    <t>flag_left_sl</t>
-  </si>
-  <si>
-    <t>left_yn,num_left</t>
-  </si>
-  <si>
-    <t>left_yn != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(num_left)</t>
-  </si>
-  <si>
-    <t>flag_left_hhsize</t>
-  </si>
-  <si>
-    <t>num_left,hh_size</t>
-  </si>
-  <si>
-    <t>num_left &lt; hh_size</t>
-  </si>
-  <si>
-    <t>flag_left_outlier</t>
-  </si>
-  <si>
-    <t>num_left</t>
-  </si>
-  <si>
-    <t>num_left &lt; 10</t>
-  </si>
-  <si>
     <t>flag_analysis</t>
   </si>
   <si>
-    <t>flag_join_sl</t>
-  </si>
-  <si>
-    <t>join_yn,num_join</t>
-  </si>
-  <si>
-    <t>join_yn != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(num_join)</t>
-  </si>
-  <si>
-    <t>flag_join_hhsize</t>
-  </si>
-  <si>
-    <t>num_join,hh_size</t>
-  </si>
-  <si>
-    <t>num_join &lt; hh_size</t>
-  </si>
-  <si>
-    <t>flag_join_outlier</t>
-  </si>
-  <si>
-    <t>num_join</t>
-  </si>
-  <si>
-    <t>num_join &lt; 10</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assistant_sl1</t>
-  </si>
-  <si>
-    <t>hd_nest_rely_assistant,hd_nest_rely_assistant_num</t>
-  </si>
-  <si>
-    <t>hd_nest_rely_assistant == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(hd_nest_rely_assistant_num)</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assistant_sl2</t>
-  </si>
-  <si>
-    <t>hd_nest_rely_assistant != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(hd_nest_rely_assistant_num)</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assistive_device_sl1</t>
-  </si>
-  <si>
-    <t>hd_nest_assistive_device,hd_nest_assistive_device_num</t>
-  </si>
-  <si>
-    <t>hd_nest_assistive_device == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(hd_nest_assistive_device_num)</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assistive_device_sl2</t>
-  </si>
-  <si>
-    <t>hd_nest_assistive_device != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(hd_nest_assistive_device_num)</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assist_information_sl1</t>
-  </si>
-  <si>
-    <t>hd_nest_assist_information,hd_nest_assist_information_num</t>
-  </si>
-  <si>
-    <t>flag_hd_nest_assist_information_sl2</t>
-  </si>
-  <si>
     <t>flag_heatlh_barriers_dontknow</t>
   </si>
   <si>
@@ -550,66 +208,6 @@
     <t>!.is_greater_than_three_selection(health_barriers)</t>
   </si>
   <si>
-    <t>flag_health_travel_time_sl1</t>
-  </si>
-  <si>
-    <t>health_travel_time,health_travel_time_minutes</t>
-  </si>
-  <si>
-    <t>health_travel_time == 'num_minutes'</t>
-  </si>
-  <si>
-    <t>!is.na(health_travel_time_minutes)</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl2</t>
-  </si>
-  <si>
-    <t>health_travel_time != 'num_minutes'</t>
-  </si>
-  <si>
-    <t>is.na(health_travel_time_minutes)</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl3</t>
-  </si>
-  <si>
-    <t>health_travel_time,health_travel_time_range</t>
-  </si>
-  <si>
-    <t>health_travel_time == 'range'</t>
-  </si>
-  <si>
-    <t>!is.na(health_travel_time_range)</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl4</t>
-  </si>
-  <si>
-    <t>health_travel_time != 'range'</t>
-  </si>
-  <si>
-    <t>is.na(health_travel_time_range)</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl5</t>
-  </si>
-  <si>
-    <t>health_travel_time == 'prefer_not_to_answer'</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl6</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl7</t>
-  </si>
-  <si>
-    <t>health_travel_time == 'dont_know'</t>
-  </si>
-  <si>
-    <t>flag_health_travel_time_sl8</t>
-  </si>
-  <si>
     <t>flag_fcs_cereal_missing</t>
   </si>
   <si>
@@ -1159,207 +757,9 @@
     <t>fsl_rcsi_mealadult == 0</t>
   </si>
   <si>
-    <t>flag_hhs_no_nofood</t>
-  </si>
-  <si>
-    <t>fsl_hhs_nofoodhh,fsl_hhs_nofoodhh_freq</t>
-  </si>
-  <si>
-    <t>fsl_hhs_nofoodhh == 'no'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_hhs_nofoodhh_freq)</t>
-  </si>
-  <si>
-    <t>flag_hhs_yes_nofood</t>
-  </si>
-  <si>
-    <t>fsl_hhs_nofoodhh == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_hhs_nofoodhh_freq)</t>
-  </si>
-  <si>
-    <t>flag_hhs_no_sleephungry</t>
-  </si>
-  <si>
-    <t>fsl_hhs_sleephungry,fsl_hhs_sleephungry_freq</t>
-  </si>
-  <si>
-    <t>fsl_hhs_sleephungry == 'no'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_hhs_sleephungry_freq)</t>
-  </si>
-  <si>
-    <t>flag_hhs_yes_sleephungry</t>
-  </si>
-  <si>
-    <t>fsl_hhs_sleephungry == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_hhs_sleephungry_freq)</t>
-  </si>
-  <si>
-    <t>flag_hhs_no_alldaynight</t>
-  </si>
-  <si>
-    <t>fsl_hhs_alldaynight,fsl_hhs_alldaynight_freq</t>
-  </si>
-  <si>
-    <t>fsl_hhs_alldaynight == 'no'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_hhs_alldaynight_freq)</t>
-  </si>
-  <si>
-    <t>flag_hhs_yes_alldaynight</t>
-  </si>
-  <si>
-    <t>fsl_hhs_alldaynight == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_hhs_alldaynight_freq)</t>
-  </si>
-  <si>
-    <t>flag_food_source_assistance</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources,fsl_second_food_sources,fsl_third_food_sources,fsl_food_cash_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fsl_food_cash_voucher == 'yes', </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fsl_first_food_sources == 'hum_assistance' | fsl_second_food_sources == 'hum_assistance' | fsl_third_food_sources == 'hum_assistance' </t>
-  </si>
-  <si>
-    <t>flag_first_food_source_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources,fsl_first_food_sources_other</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_first_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_first_food_source_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_first_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_second_food_source_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources,fsl_second_food_sources_other</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_second_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_second_food_source_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_second_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_third_food_source_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_third_food_sources,fsl_third_food_sources_other</t>
-  </si>
-  <si>
-    <t>fsl_third_food_sources == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_third_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_third_food_source_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_third_food_sources != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_third_food_sources)</t>
-  </si>
-  <si>
-    <t>flag_first_second_food_source</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources,fsl_second_food_sources</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources != fsl_second_food_sources</t>
-  </si>
-  <si>
-    <t>flag_first_third_food_source</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources,fsl_third_food_sources</t>
-  </si>
-  <si>
-    <t>fsl_first_food_sources != fsl_third_food_sources</t>
-  </si>
-  <si>
-    <t>flag_second_third_food_source</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources,fsl_third_food_sources</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources != fsl_third_food_sources</t>
-  </si>
-  <si>
-    <t>flag_food_source_none</t>
-  </si>
-  <si>
     <t>fsl_first_food_sources</t>
   </si>
   <si>
-    <t>fsl_first_food_sources != 'none'</t>
-  </si>
-  <si>
-    <t>flag_food_source_first_third_none_sl</t>
-  </si>
-  <si>
-    <t>fsl_second_food_sources == 'none'</t>
-  </si>
-  <si>
-    <t>flag_food_source_barrier_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_food_sources_barriers,fsl_food_sources_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', fsl_food_sources_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_food_sources_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_food_source_barrier_other_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', fsl_food_sources_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(fsl_food_sources_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_food_source_barrier_dontknow_count</t>
   </si>
   <si>
@@ -1390,48 +790,6 @@
     <t>!.is_greater_than_three_selection(fsl_food_sources_barriers)</t>
   </si>
   <si>
-    <t>flag_food_water_prep_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_hh_clean_water_preparation,fsl_hh_clean_water_preparation_other</t>
-  </si>
-  <si>
-    <t>fsl_hh_clean_water_preparation == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_hh_clean_water_preparation_other)</t>
-  </si>
-  <si>
-    <t>flag_food_water_prep_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_hh_clean_water_preparation != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_hh_clean_water_preparation_other)</t>
-  </si>
-  <si>
-    <t>flag_cooking_energy_access_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_hh_access_cooking_energy,fsl_hh_access_cooking_energy_other</t>
-  </si>
-  <si>
-    <t>fsl_hh_access_cooking_energy == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_hh_access_cooking_energy_other)</t>
-  </si>
-  <si>
-    <t>flag_cooking_energy_access_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_hh_access_cooking_energy != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_hh_access_cooking_energy_other)</t>
-  </si>
-  <si>
     <t>flag_num_meals_above5_outlier</t>
   </si>
   <si>
@@ -1450,144 +808,6 @@
     <t>fsl_num_meals_under_5 &lt;= 5</t>
   </si>
   <si>
-    <t>flag_first_income_type_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types,fsl_first_income_types_other</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_first_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_first_income_type_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_first_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_second_income_type_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_second_income_types,fsl_second_income_types_other</t>
-  </si>
-  <si>
-    <t>fsl_second_income_types == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_second_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_second_income_type_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_second_income_types != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_second_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_third_income_type_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_third_income_types,fsl_third_income_types_other</t>
-  </si>
-  <si>
-    <t>fsl_third_income_types == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_third_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_third_income_type_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_third_income_types != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_third_income_types_other)</t>
-  </si>
-  <si>
-    <t>flag_first_second_income_nondup</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types,fsl_second_income_types</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_second_income_types)</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types != fsl_second_income_types</t>
-  </si>
-  <si>
-    <t>flag_first_third_income_nondup</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types,fsl_third_income_types</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_third_income_types)</t>
-  </si>
-  <si>
-    <t>fsl_first_income_types != fsl_third_income_types</t>
-  </si>
-  <si>
-    <t>flag_second_third_income_nondup</t>
-  </si>
-  <si>
-    <t>fsl_second_income_types,fsl_third_income_types</t>
-  </si>
-  <si>
-    <t>fsl_second_income_types != fsl_third_income_types</t>
-  </si>
-  <si>
-    <t>flag_fsl_assistance_modality_other_sl1</t>
-  </si>
-  <si>
-    <t>fsl_assistance_modality,fsl_assistance_modality_other</t>
-  </si>
-  <si>
-    <t>fsl_assistance_modality == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_assistance_modality_other)</t>
-  </si>
-  <si>
-    <t>flag_fsl_assistance_modality_other_sl2</t>
-  </si>
-  <si>
-    <t>fsl_assistance_modality != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_assistance_modality_other)</t>
-  </si>
-  <si>
-    <t>flag_fsl_assistance_sl1</t>
-  </si>
-  <si>
-    <t>fsl_food_cash_voucher,fsl_assistance_modality</t>
-  </si>
-  <si>
-    <t>fsl_food_cash_voucher=='yes'</t>
-  </si>
-  <si>
-    <t>!is.na(fsl_assistance_modality)</t>
-  </si>
-  <si>
-    <t>flag_fsl_assistance_sl2</t>
-  </si>
-  <si>
-    <t>fsl_food_cash_voucher!='yes'</t>
-  </si>
-  <si>
-    <t>is.na(fsl_assistance_modality)</t>
-  </si>
-  <si>
     <t>flag_fsl_assistance_modality_dontknow_count</t>
   </si>
   <si>
@@ -1618,48 +838,6 @@
     <t>!.is_greater_than_three_selection(fsl_assistance_modality)</t>
   </si>
   <si>
-    <t>flag_market_barriers_other_sl1</t>
-  </si>
-  <si>
-    <t>market_barriers,market_barriers_other</t>
-  </si>
-  <si>
-    <t>market_barriers == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(market_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_market_barriers_other_sl2</t>
-  </si>
-  <si>
-    <t>market_barriers != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(market_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_purchase_barriers_other_sl1</t>
-  </si>
-  <si>
-    <t>purchase_barriers,purchase_barriers_other</t>
-  </si>
-  <si>
-    <t>purchase_barriers == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(purchase_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_purchase_barriers_other_sl2</t>
-  </si>
-  <si>
-    <t>purchase_barriers != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(purchase_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_sd_litre</t>
   </si>
   <si>
@@ -1756,69 +934,6 @@
     <t>wash_water_interruption_num_days &lt; 4</t>
   </si>
   <si>
-    <t>flag_water_source_sl1</t>
-  </si>
-  <si>
-    <t>wash_water_source,wash_water_source_other</t>
-  </si>
-  <si>
-    <t>wash_water_source == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_water_source_other)</t>
-  </si>
-  <si>
-    <t>flag_water_source_s2</t>
-  </si>
-  <si>
-    <t>wash_water_source != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(wash_water_source_other)</t>
-  </si>
-  <si>
-    <t>flag_other_water_sources_sl</t>
-  </si>
-  <si>
-    <t>wash_other_water_sources,wash_different_water_sources</t>
-  </si>
-  <si>
-    <t>wash_other_water_sources == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_different_water_sources)</t>
-  </si>
-  <si>
-    <t>flag_other_water_sources_sl2</t>
-  </si>
-  <si>
-    <t>wash_other_water_sources != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(wash_different_water_sources)</t>
-  </si>
-  <si>
-    <t>flag_other_different_water_sources_sl</t>
-  </si>
-  <si>
-    <t>wash_different_water_sources,wash_different_water_sources_other</t>
-  </si>
-  <si>
-    <t>wash_different_water_sources == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_different_water_sources_other)</t>
-  </si>
-  <si>
-    <t>flag_other_different_water_sources_sl2</t>
-  </si>
-  <si>
-    <t>wash_different_water_sources != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(wash_different_water_sources_other)</t>
-  </si>
-  <si>
     <t>flag_wash_different_water_sources_dontknow_count</t>
   </si>
   <si>
@@ -1846,72 +961,6 @@
     <t>is.na(wash_third_water_source_usage)</t>
   </si>
   <si>
-    <t>flag_other_first_usage_sl</t>
-  </si>
-  <si>
-    <t>wash_first_water_source_usage,wash_first_water_source_usage_other</t>
-  </si>
-  <si>
-    <t>wash_first_water_source_usage == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_first_water_source_usage_other)</t>
-  </si>
-  <si>
-    <t>flag_other_first_usage_sl2</t>
-  </si>
-  <si>
-    <t>wash_first_water_source_usage != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(wash_first_water_source_usage_other)</t>
-  </si>
-  <si>
-    <t>flag_other_second_usage_sl</t>
-  </si>
-  <si>
-    <t>wash_second_water_source_usage,wash_second_water_source_usage_other</t>
-  </si>
-  <si>
-    <t>wash_second_water_source_usage == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_second_water_source_usage_other)</t>
-  </si>
-  <si>
-    <t>flag_other_second_usage_sl2</t>
-  </si>
-  <si>
-    <t>wash_second_water_source_usage != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(wash_second_water_source_usage_other)</t>
-  </si>
-  <si>
-    <t>flag_collect_time_int_sl</t>
-  </si>
-  <si>
-    <t>wash_water_collect_time,wash_water_collect_time_int</t>
-  </si>
-  <si>
-    <t>wash_water_collect_time == 'num_minutes'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_water_collect_time_int)</t>
-  </si>
-  <si>
-    <t>flag_collect_time_range_sl</t>
-  </si>
-  <si>
-    <t>wash_water_collect_time,wash_water_collect_time_range</t>
-  </si>
-  <si>
-    <t>wash_water_collect_time == 'dont_know'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_water_collect_time_range)</t>
-  </si>
-  <si>
     <t>flag_piped_time_collection1</t>
   </si>
   <si>
@@ -1957,45 +1006,6 @@
     <t>wash_water_source != 'prefer_not_to_answer'</t>
   </si>
   <si>
-    <t>flag_water_treatment_other_sl</t>
-  </si>
-  <si>
-    <t>wash_water_treatment,wash_water_treatment_other</t>
-  </si>
-  <si>
-    <t>wash_water_treatment == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_water_treatment_other)</t>
-  </si>
-  <si>
-    <t>flag_water_source_interrupt_sl1</t>
-  </si>
-  <si>
-    <t>wash_water_source,wash_water_interruption</t>
-  </si>
-  <si>
-    <t>!is.na(wash_water_interruption)</t>
-  </si>
-  <si>
-    <t>flag_water_source_interrupt_sl2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wash_water_source != 'piped_dwelling' &amp; wash_water_source != 'piped_compound' </t>
-  </si>
-  <si>
-    <t>is.na(wash_water_interruption)</t>
-  </si>
-  <si>
-    <t>flag_water_interruption_days_sl</t>
-  </si>
-  <si>
-    <t>wash_water_interruption,wash_water_interruption_num_days</t>
-  </si>
-  <si>
-    <t>wash_water_interruption == 'yes'</t>
-  </si>
-  <si>
     <t>!is.na(wash_water_interruption_num_days)</t>
   </si>
   <si>
@@ -2014,27 +1024,6 @@
     <t>wash_water_interruption_num_days &lt;= 15</t>
   </si>
   <si>
-    <t>flag_wash_containers_sl1</t>
-  </si>
-  <si>
-    <t>wash_containers,wash_num_containers</t>
-  </si>
-  <si>
-    <t>wash_containers == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_num_containers)</t>
-  </si>
-  <si>
-    <t>flag_wash_containers_sl2</t>
-  </si>
-  <si>
-    <t>wash_containers != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(wash_num_containers)</t>
-  </si>
-  <si>
     <t>flag_high_container</t>
   </si>
   <si>
@@ -2080,27 +1069,6 @@
     <t>wash_wise_hands != 'never'</t>
   </si>
   <si>
-    <t>flag_mosquito_net_sl1</t>
-  </si>
-  <si>
-    <t>wash_mosquito_net,wash_source_mosquito_net</t>
-  </si>
-  <si>
-    <t>wash_mosquito_net == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(wash_source_mosquito_net)</t>
-  </si>
-  <si>
-    <t>flag_mosquito_net_sl2</t>
-  </si>
-  <si>
-    <t>wash_mosquito_net != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(wash_source_mosquito_net)</t>
-  </si>
-  <si>
     <t>flag_mnet_nochild_sl</t>
   </si>
   <si>
@@ -2137,27 +1105,12 @@
     <t>wash_toilet_facility == 'bucket'</t>
   </si>
   <si>
-    <t>flag_share_num_toilet_sl1</t>
-  </si>
-  <si>
     <t>wash_share_toilet_facility,wash_num_share_toilet</t>
   </si>
   <si>
     <t>wash_share_toilet_facility == 'yes'</t>
   </si>
   <si>
-    <t>!is.na(wash_num_share_toilet)</t>
-  </si>
-  <si>
-    <t>flag_share_num_toilet_sl2</t>
-  </si>
-  <si>
-    <t>wash_share_toilet_facility != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(wash_num_share_toilet)</t>
-  </si>
-  <si>
     <t>flag_share_toilet_one</t>
   </si>
   <si>
@@ -2185,63 +1138,15 @@
     <t>!is.na(dimension_measure)</t>
   </si>
   <si>
-    <t>flag_shelter_length_sl1</t>
-  </si>
-  <si>
-    <t>shape_shelter,length_long</t>
-  </si>
-  <si>
-    <t>shape_shelter == 'rectangle'</t>
-  </si>
-  <si>
     <t>!is.na(length_long)</t>
   </si>
   <si>
-    <t>flag_shelter_length_sl2</t>
-  </si>
-  <si>
-    <t>shape_shelter != 'rectangle'</t>
-  </si>
-  <si>
-    <t>is.na(length_long)</t>
-  </si>
-  <si>
-    <t>flag_shelter_width_sl1</t>
-  </si>
-  <si>
-    <t>shape_shelter,width_larg</t>
-  </si>
-  <si>
     <t>!is.na(width_larg)</t>
   </si>
   <si>
-    <t>flag_shelter_width_sl2</t>
-  </si>
-  <si>
-    <t>is.na(width_larg)</t>
-  </si>
-  <si>
-    <t>flag_shelter_diameter_sl1</t>
-  </si>
-  <si>
-    <t>shape_shelter,diameter</t>
-  </si>
-  <si>
-    <t>shape_shelter == 'circle'</t>
-  </si>
-  <si>
     <t>!is.na(diameter)</t>
   </si>
   <si>
-    <t>flag_shelter_diameter_sl2</t>
-  </si>
-  <si>
-    <t>shape_shelter != 'circle'</t>
-  </si>
-  <si>
-    <t>is.na(diameter)</t>
-  </si>
-  <si>
     <t>flag_dimension_length</t>
   </si>
   <si>
@@ -2287,27 +1192,6 @@
     <t>diameter &lt; 100</t>
   </si>
   <si>
-    <t>flag_other_shelter_type_sl1</t>
-  </si>
-  <si>
-    <t>shelter_type,shelter_type_other</t>
-  </si>
-  <si>
-    <t>shelter_type == 'other'</t>
-  </si>
-  <si>
-    <t>!is.na(shelter_type_other)</t>
-  </si>
-  <si>
-    <t>flag_other_shelter_type_sl2</t>
-  </si>
-  <si>
-    <t>shelter_type != 'other'</t>
-  </si>
-  <si>
-    <t>is.na(shelter_type_other)</t>
-  </si>
-  <si>
     <t>flag_issues_no_shelter</t>
   </si>
   <si>
@@ -2320,27 +1204,6 @@
     <t>is.na(shelter_issues)</t>
   </si>
   <si>
-    <t>flag_shelter_issues_other_sl1</t>
-  </si>
-  <si>
-    <t>shelter_issues,shelter_issues_other</t>
-  </si>
-  <si>
-    <t>grepl('other', shelter_issues, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(shelter_issues_other)</t>
-  </si>
-  <si>
-    <t>flag_shelter_issues_other_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', shelter_issues, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(shelter_issues_other)</t>
-  </si>
-  <si>
     <t>flag_shelter_issues_dontknow_count</t>
   </si>
   <si>
@@ -2365,45 +1228,6 @@
     <t>grepl('none', shelter_issues,ignore.case=TRUE)</t>
   </si>
   <si>
-    <t>flag_cooking_abilities_barriers_sl1</t>
-  </si>
-  <si>
-    <t>cooking_abilities,cooking_barriers</t>
-  </si>
-  <si>
-    <t>cooking_abilities == 'yes_w_issues' | cooking_abilities == 'no'</t>
-  </si>
-  <si>
-    <t>!is.na(cooking_barriers)</t>
-  </si>
-  <si>
-    <t>flag_cooking_abilities_barriers_sl2</t>
-  </si>
-  <si>
-    <t>cooking_abilities == 'yes'</t>
-  </si>
-  <si>
-    <t>flag_other_cooking_barriers_sl1</t>
-  </si>
-  <si>
-    <t>cooking_barriers,cooking_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', cooking_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(cooking_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_other_cooking_barriers_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', cooking_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(cooking_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_cooking_barriers_pnta_count</t>
   </si>
   <si>
@@ -2416,48 +1240,6 @@
     <t>!.is_greater_than_one_selection(cooking_barriers)</t>
   </si>
   <si>
-    <t>flag_sleeping_abilities_barriers_sl1</t>
-  </si>
-  <si>
-    <t>sleeping_abilities,sleeping_barriers</t>
-  </si>
-  <si>
-    <t>sleeping_abilities != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(sleeping_barriers)</t>
-  </si>
-  <si>
-    <t>flag_sleeping_abilities_barriers_sl2</t>
-  </si>
-  <si>
-    <t>sleeping_abilities == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(sleeping_barriers)</t>
-  </si>
-  <si>
-    <t>flag_other_sleeping_barriers_sl1</t>
-  </si>
-  <si>
-    <t>sleeping_barriers,sleeping_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', sleeping_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(sleeping_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_other_sleeping_barriers_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', sleeping_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(sleeping_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_sleeping_barriers_pnta_count</t>
   </si>
   <si>
@@ -2470,48 +1252,6 @@
     <t>!.is_greater_than_one_selection(sleeping_barriers)</t>
   </si>
   <si>
-    <t>flag_storing_abilities_barriers_sl1</t>
-  </si>
-  <si>
-    <t>storing_abilities,storing_barriers</t>
-  </si>
-  <si>
-    <t>storing_abilities != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(storing_barriers)</t>
-  </si>
-  <si>
-    <t>flag_storing_abilities_barriers_sl2</t>
-  </si>
-  <si>
-    <t>storing_abilities == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(storing_barriers)</t>
-  </si>
-  <si>
-    <t>flag_other_storing_barriers_sl1</t>
-  </si>
-  <si>
-    <t>storing_barriers,storing_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', storing_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(storing_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_other_storing_barriers_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', storing_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(storing_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_storing_barriers_pnta_count</t>
   </si>
   <si>
@@ -2524,48 +1264,6 @@
     <t>!.is_greater_than_one_selection(storing_barriers)</t>
   </si>
   <si>
-    <t>flag_lighting_abilities_barriers_sl1</t>
-  </si>
-  <si>
-    <t>lighting_abilities,lighting_barriers</t>
-  </si>
-  <si>
-    <t>lighting_abilities != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(lighting_barriers)</t>
-  </si>
-  <si>
-    <t>flag_lighting_abilities_barriers_sl2</t>
-  </si>
-  <si>
-    <t>lighting_abilities == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(lighting_barriers)</t>
-  </si>
-  <si>
-    <t>flag_other_lighting_barriers_sl1</t>
-  </si>
-  <si>
-    <t>lighting_barriers,lighting_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', lighting_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(lighting_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_other_lighting_barriers_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', lighting_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(lighting_barriers_other)</t>
-  </si>
-  <si>
     <t>flag_lighting_barriers_pnta_count</t>
   </si>
   <si>
@@ -2576,48 +1274,6 @@
   </si>
   <si>
     <t>!.is_greater_than_one_selection(lighting_barriers)</t>
-  </si>
-  <si>
-    <t>flag_hygiene_abilities_barriers_sl1</t>
-  </si>
-  <si>
-    <t>hygiene_abilities,hygiene_barriers</t>
-  </si>
-  <si>
-    <t>hygiene_abilities != 'yes'</t>
-  </si>
-  <si>
-    <t>is.na(hygiene_barriers)</t>
-  </si>
-  <si>
-    <t>flag_hygiene_abilities_barriers_sl2</t>
-  </si>
-  <si>
-    <t>hygiene_abilities == 'yes'</t>
-  </si>
-  <si>
-    <t>!is.na(hygiene_barriers)</t>
-  </si>
-  <si>
-    <t>flag_other_hygiene_barriers_sl1</t>
-  </si>
-  <si>
-    <t>hygiene_barriers,hygiene_barriers_other</t>
-  </si>
-  <si>
-    <t>grepl('other', hygiene_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>!is.na(hygiene_barriers_other)</t>
-  </si>
-  <si>
-    <t>flag_other_hygiene_barriers_sl2</t>
-  </si>
-  <si>
-    <t>!grepl('other', hygiene_barriers, ignore.case = TRUE)</t>
-  </si>
-  <si>
-    <t>is.na(hygiene_barriers_other)</t>
   </si>
   <si>
     <t>flag_hygiene_barriers_pnta_count</t>
@@ -4138,11 +2794,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.42578125" customWidth="1"/>
     <col min="3" max="3" width="69.85546875" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="62" customWidth="1"/>
@@ -4422,16 +3078,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -4442,16 +3098,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
         <v>52</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>53</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -4462,16 +3118,16 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -4485,13 +3141,13 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -4502,16 +3158,16 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
         <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" t="s">
-        <v>61</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -4522,16 +3178,16 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
         <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -4542,16 +3198,16 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -4562,19 +3218,19 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4582,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4602,19 +3258,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4622,19 +3278,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4642,19 +3298,19 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4662,16 +3318,16 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -4682,13 +3338,13 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
         <v>86</v>
       </c>
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
+      <c r="D27" t="b">
+        <v>1</v>
       </c>
       <c r="E27" t="s">
         <v>89</v>
@@ -4705,13 +3361,13 @@
         <v>90</v>
       </c>
       <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s">
-        <v>89</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -4722,16 +3378,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
         <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>95</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -4742,16 +3398,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>98</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -4762,16 +3418,16 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -4782,16 +3438,16 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
         <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>104</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -4802,16 +3458,16 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
         <v>105</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>106</v>
-      </c>
-      <c r="D33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" t="s">
-        <v>108</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -4822,13 +3478,13 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" t="s">
         <v>109</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>89</v>
       </c>
       <c r="E34" t="s">
         <v>110</v>
@@ -4848,10 +3504,10 @@
         <v>112</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -4862,16 +3518,16 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -4882,16 +3538,16 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -4902,16 +3558,16 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -4922,16 +3578,16 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
@@ -4942,16 +3598,16 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
@@ -4962,16 +3618,16 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
@@ -4982,16 +3638,16 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" t="b">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="D42" t="s">
+        <v>139</v>
       </c>
       <c r="E42" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
@@ -5002,19 +3658,19 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" t="b">
-        <v>1</v>
+        <v>108</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
       </c>
       <c r="E43" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,16 +3678,16 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -5042,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" t="b">
-        <v>1</v>
+        <v>116</v>
+      </c>
+      <c r="D45" t="s">
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F45" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,19 +3718,19 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
-      </c>
-      <c r="D46" t="b">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F46" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5082,16 +3738,16 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E47" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F47" t="s">
         <v>13</v>
@@ -5102,16 +3758,16 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
@@ -5122,16 +3778,16 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
@@ -5142,19 +3798,19 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5162,19 +3818,19 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>161</v>
-      </c>
-      <c r="D51" t="s">
-        <v>148</v>
+        <v>167</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -5182,19 +3838,19 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E52" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -5202,16 +3858,16 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" t="s">
-        <v>165</v>
+        <v>174</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -5222,16 +3878,16 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C54" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -5242,19 +3898,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" t="s">
-        <v>170</v>
+        <v>181</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -5262,16 +3918,16 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -5282,19 +3938,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,16 +3958,16 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>177</v>
+        <v>757</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
@@ -5322,16 +3978,16 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -5342,16 +3998,16 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
+      </c>
+      <c r="D60" t="s">
+        <v>197</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -5362,16 +4018,16 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
+      </c>
+      <c r="D61" t="s">
+        <v>200</v>
       </c>
       <c r="E61" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
@@ -5382,16 +4038,16 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>190</v>
+        <v>80</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
@@ -5402,16 +4058,16 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C63" t="s">
-        <v>176</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -5422,16 +4078,16 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -5442,16 +4098,16 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>176</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>193</v>
+        <v>73</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -5462,16 +4118,16 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" t="s">
-        <v>197</v>
+        <v>213</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -5482,16 +4138,16 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" t="s">
-        <v>201</v>
+        <v>216</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
@@ -5502,19 +4158,19 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F68" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5522,19 +4178,19 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D69" t="b">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="F69" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,19 +4198,19 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D70" t="s">
-        <v>211</v>
+        <v>224</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F70" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5562,19 +4218,19 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C71" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F71" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5582,19 +4238,19 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C72" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5602,16 +4258,16 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C73" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D73" t="b">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
@@ -5622,16 +4278,16 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -5642,16 +4298,16 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D75" t="b">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
@@ -5662,19 +4318,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C76" t="s">
-        <v>220</v>
-      </c>
-      <c r="D76" t="b">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="D76" t="s">
+        <v>242</v>
       </c>
       <c r="E76" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5682,16 +4338,16 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C77" t="s">
-        <v>229</v>
-      </c>
-      <c r="D77" t="b">
-        <v>1</v>
+        <v>246</v>
+      </c>
+      <c r="D77" t="s">
+        <v>247</v>
       </c>
       <c r="E77" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
@@ -5702,16 +4358,16 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C78" t="s">
-        <v>229</v>
-      </c>
-      <c r="D78" t="b">
-        <v>1</v>
+        <v>246</v>
+      </c>
+      <c r="D78" t="s">
+        <v>250</v>
       </c>
       <c r="E78" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -5722,16 +4378,16 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E79" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -5742,16 +4398,16 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C80" t="s">
-        <v>238</v>
-      </c>
-      <c r="D80" t="s">
-        <v>239</v>
+        <v>246</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
@@ -5762,16 +4418,16 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
+        <v>256</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -5782,16 +4438,16 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C82" t="s">
-        <v>246</v>
-      </c>
-      <c r="D82" t="s">
-        <v>247</v>
+        <v>259</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
@@ -5802,16 +4458,16 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C83" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E83" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -5822,16 +4478,16 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C84" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E84" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -5842,16 +4498,16 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C85" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E85" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F85" t="s">
         <v>13</v>
@@ -5862,16 +4518,16 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C86" t="s">
         <v>262</v>
       </c>
-      <c r="D86" t="s">
-        <v>263</v>
+      <c r="D86" t="b">
+        <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F86" t="s">
         <v>13</v>
@@ -5882,16 +4538,16 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
-      </c>
-      <c r="D87" t="s">
-        <v>267</v>
+        <v>272</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
@@ -5902,16 +4558,16 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C88" t="s">
-        <v>234</v>
-      </c>
-      <c r="D88" t="s">
-        <v>270</v>
+        <v>272</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
@@ -5922,16 +4578,16 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" t="s">
         <v>272</v>
       </c>
-      <c r="C89" t="s">
-        <v>238</v>
-      </c>
-      <c r="D89" t="s">
-        <v>273</v>
+      <c r="D89" t="b">
+        <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
@@ -5942,16 +4598,16 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C90" t="s">
-        <v>242</v>
-      </c>
-      <c r="D90" t="s">
-        <v>276</v>
+        <v>279</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
@@ -5962,16 +4618,16 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C91" t="s">
-        <v>246</v>
-      </c>
-      <c r="D91" t="s">
-        <v>279</v>
+        <v>282</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
@@ -5982,16 +4638,16 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C92" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D92" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E92" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
@@ -6002,16 +4658,16 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D93" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E93" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
@@ -6022,16 +4678,16 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C94" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E94" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
@@ -6042,16 +4698,16 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="D95" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
@@ -6062,16 +4718,16 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C96" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E96" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
@@ -6082,19 +4738,19 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>296</v>
-      </c>
-      <c r="C97" t="s">
-        <v>297</v>
+        <v>303</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="D97" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E97" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F97" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6102,19 +4758,19 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>300</v>
-      </c>
-      <c r="C98" t="s">
-        <v>301</v>
+        <v>307</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F98" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -6122,19 +4778,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>303</v>
-      </c>
-      <c r="C99" t="s">
-        <v>304</v>
+        <v>309</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="D99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E99" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F99" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -6142,16 +4798,16 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C100" t="s">
-        <v>308</v>
-      </c>
-      <c r="D100" t="b">
-        <v>1</v>
+        <v>313</v>
+      </c>
+      <c r="D100" t="s">
+        <v>314</v>
       </c>
       <c r="E100" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -6162,16 +4818,16 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C101" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D101" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E101" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
@@ -6182,19 +4838,19 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C102" t="s">
+        <v>313</v>
+      </c>
+      <c r="D102" t="s">
+        <v>319</v>
+      </c>
+      <c r="E102" t="s">
         <v>315</v>
       </c>
-      <c r="D102" t="b">
-        <v>1</v>
-      </c>
-      <c r="E102" t="s">
-        <v>316</v>
-      </c>
       <c r="F102" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -6202,16 +4858,16 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C103" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E103" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
@@ -6222,19 +4878,19 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C104" t="s">
+        <v>313</v>
+      </c>
+      <c r="D104" t="s">
+        <v>324</v>
+      </c>
+      <c r="E104" t="s">
         <v>322</v>
       </c>
-      <c r="D104" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" t="s">
-        <v>323</v>
-      </c>
       <c r="F104" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -6242,16 +4898,16 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C105" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D105" t="b">
-        <v>1</v>
+        <v>313</v>
+      </c>
+      <c r="D105" t="s">
+        <v>326</v>
       </c>
       <c r="E105" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
@@ -6262,16 +4918,16 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C106" t="s">
+        <v>329</v>
+      </c>
+      <c r="D106" t="s">
         <v>327</v>
       </c>
-      <c r="D106" t="b">
-        <v>1</v>
-      </c>
       <c r="E106" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
@@ -6282,13 +4938,13 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
+        <v>331</v>
+      </c>
+      <c r="C107" t="s">
         <v>329</v>
       </c>
-      <c r="C107" t="s">
-        <v>330</v>
-      </c>
       <c r="D107" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E107" t="s">
         <v>332</v>
@@ -6305,10 +4961,10 @@
         <v>333</v>
       </c>
       <c r="C108" t="s">
-        <v>330</v>
-      </c>
-      <c r="D108" t="s">
         <v>334</v>
+      </c>
+      <c r="D108" t="b">
+        <v>1</v>
       </c>
       <c r="E108" t="s">
         <v>335</v>
@@ -6325,7 +4981,7 @@
         <v>336</v>
       </c>
       <c r="C109" t="s">
-        <v>214</v>
+        <v>334</v>
       </c>
       <c r="D109" t="b">
         <v>1</v>
@@ -6347,14 +5003,14 @@
       <c r="C110" t="s">
         <v>339</v>
       </c>
-      <c r="D110" t="b">
-        <v>1</v>
+      <c r="D110" t="s">
+        <v>340</v>
       </c>
       <c r="E110" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -6362,19 +5018,19 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
-      </c>
-      <c r="D111" t="b">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="D111" t="s">
+        <v>340</v>
       </c>
       <c r="E111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -6382,19 +5038,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" t="s">
-        <v>207</v>
-      </c>
-      <c r="D112" t="b">
-        <v>1</v>
+        <v>346</v>
+      </c>
+      <c r="D112" t="s">
+        <v>340</v>
       </c>
       <c r="E112" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -6402,16 +5058,16 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C113" t="s">
-        <v>347</v>
-      </c>
-      <c r="D113" t="b">
-        <v>1</v>
+        <v>349</v>
+      </c>
+      <c r="D113" t="s">
+        <v>350</v>
       </c>
       <c r="E113" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F113" t="s">
         <v>13</v>
@@ -6422,16 +5078,16 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
-      </c>
-      <c r="D114" t="b">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="D114" t="s">
+        <v>354</v>
       </c>
       <c r="E114" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F114" t="s">
         <v>13</v>
@@ -6442,16 +5098,16 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
-      </c>
-      <c r="D115" t="b">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="D115" t="s">
+        <v>357</v>
       </c>
       <c r="E115" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F115" t="s">
         <v>13</v>
@@ -6462,16 +5118,16 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C116" t="s">
+        <v>353</v>
+      </c>
+      <c r="D116" t="s">
+        <v>359</v>
+      </c>
+      <c r="E116" t="s">
         <v>355</v>
-      </c>
-      <c r="D116" t="b">
-        <v>1</v>
-      </c>
-      <c r="E116" t="s">
-        <v>356</v>
       </c>
       <c r="F116" t="s">
         <v>13</v>
@@ -6482,16 +5138,16 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C117" t="s">
-        <v>358</v>
-      </c>
-      <c r="D117" t="b">
-        <v>1</v>
+        <v>360</v>
+      </c>
+      <c r="D117" t="s">
+        <v>361</v>
       </c>
       <c r="E117" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F117" t="s">
         <v>13</v>
@@ -6502,16 +5158,16 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C118" t="s">
-        <v>361</v>
-      </c>
-      <c r="D118" t="b">
-        <v>1</v>
+        <v>365</v>
+      </c>
+      <c r="D118" t="s">
+        <v>366</v>
       </c>
       <c r="E118" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
@@ -6522,16 +5178,16 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C119" t="s">
-        <v>364</v>
-      </c>
-      <c r="D119" t="b">
-        <v>1</v>
+        <v>365</v>
+      </c>
+      <c r="D119" t="s">
+        <v>369</v>
       </c>
       <c r="E119" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F119" t="s">
         <v>13</v>
@@ -6542,16 +5198,16 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s">
-        <v>367</v>
-      </c>
-      <c r="D120" t="b">
-        <v>1</v>
+        <v>375</v>
+      </c>
+      <c r="D120" t="s">
+        <v>371</v>
       </c>
       <c r="E120" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -6562,16 +5218,16 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
+        <v>377</v>
+      </c>
+      <c r="D121" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" t="s">
         <v>370</v>
-      </c>
-      <c r="D121" t="b">
-        <v>1</v>
-      </c>
-      <c r="E121" t="s">
-        <v>371</v>
       </c>
       <c r="F121" t="s">
         <v>13</v>
@@ -6582,16 +5238,16 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C122" t="s">
+        <v>379</v>
+      </c>
+      <c r="D122" t="s">
         <v>373</v>
       </c>
-      <c r="D122" t="b">
-        <v>1</v>
-      </c>
       <c r="E122" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
@@ -6602,19 +5258,19 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s">
-        <v>311</v>
-      </c>
-      <c r="D123" t="s">
-        <v>376</v>
+        <v>381</v>
+      </c>
+      <c r="D123" t="b">
+        <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F123" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6622,16 +5278,16 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C124" t="s">
-        <v>379</v>
-      </c>
-      <c r="D124" t="s">
-        <v>380</v>
+        <v>384</v>
+      </c>
+      <c r="D124" t="b">
+        <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -6642,16 +5298,16 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s">
-        <v>379</v>
-      </c>
-      <c r="D125" t="s">
-        <v>383</v>
+        <v>387</v>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F125" t="s">
         <v>13</v>
@@ -6662,16 +5318,16 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C126" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F126" t="s">
         <v>13</v>
@@ -6682,16 +5338,16 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C127" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E127" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
@@ -6702,16 +5358,16 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C128" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D128" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F128" t="s">
         <v>13</v>
@@ -6722,16 +5378,16 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
+        <v>399</v>
+      </c>
+      <c r="C129" t="s">
+        <v>394</v>
+      </c>
+      <c r="D129" t="s">
+        <v>400</v>
+      </c>
+      <c r="E129" t="s">
         <v>396</v>
-      </c>
-      <c r="C129" t="s">
-        <v>393</v>
-      </c>
-      <c r="D129" t="s">
-        <v>397</v>
-      </c>
-      <c r="E129" t="s">
-        <v>398</v>
       </c>
       <c r="F129" t="s">
         <v>13</v>
@@ -6742,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C130" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D130" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E130" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
@@ -6762,16 +5418,16 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C131" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D131" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E131" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F131" t="s">
         <v>13</v>
@@ -6782,16 +5438,16 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C132" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D132" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E132" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6802,16 +5458,16 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C133" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D133" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E133" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F133" t="s">
         <v>13</v>
@@ -6822,16 +5478,16 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C134" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D134" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E134" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F134" t="s">
         <v>13</v>
@@ -6842,19 +5498,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C135" t="s">
-        <v>418</v>
-      </c>
-      <c r="D135" t="s">
-        <v>419</v>
+        <v>422</v>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F135" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,19 +5518,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C136" t="s">
-        <v>418</v>
-      </c>
-      <c r="D136" t="s">
-        <v>422</v>
+        <v>425</v>
+      </c>
+      <c r="D136" t="b">
+        <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F136" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,19 +5538,19 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C137" t="s">
-        <v>425</v>
-      </c>
-      <c r="D137" t="s">
-        <v>413</v>
+        <v>428</v>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F137" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6902,19 +5558,19 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C138" t="s">
-        <v>428</v>
-      </c>
-      <c r="D138" t="s">
-        <v>420</v>
+        <v>431</v>
+      </c>
+      <c r="D138" t="b">
+        <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F138" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6922,19 +5578,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C139" t="s">
-        <v>431</v>
-      </c>
-      <c r="D139" t="s">
-        <v>420</v>
+        <v>434</v>
+      </c>
+      <c r="D139" t="b">
+        <v>1</v>
       </c>
       <c r="E139" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6942,19 +5598,19 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C140" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D140" t="b">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F140" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6962,19 +5618,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C141" t="s">
-        <v>431</v>
-      </c>
-      <c r="D141" t="s">
-        <v>437</v>
+        <v>440</v>
+      </c>
+      <c r="D141" t="b">
+        <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F141" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6982,16 +5638,16 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C142" t="s">
-        <v>439</v>
-      </c>
-      <c r="D142" t="s">
-        <v>440</v>
+        <v>443</v>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F142" t="s">
         <v>13</v>
@@ -7002,16 +5658,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C143" t="s">
-        <v>439</v>
-      </c>
-      <c r="D143" t="s">
-        <v>443</v>
+        <v>446</v>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F143" t="s">
         <v>13</v>
@@ -7022,16 +5678,16 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C144" t="s">
-        <v>446</v>
-      </c>
-      <c r="D144" t="s">
-        <v>447</v>
+        <v>449</v>
+      </c>
+      <c r="D144" t="b">
+        <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F144" t="s">
         <v>13</v>
@@ -7042,16 +5698,16 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C145" t="s">
-        <v>446</v>
-      </c>
-      <c r="D145" t="s">
-        <v>450</v>
+        <v>452</v>
+      </c>
+      <c r="D145" t="b">
+        <v>1</v>
       </c>
       <c r="E145" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F145" t="s">
         <v>13</v>
@@ -7062,16 +5718,16 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s">
-        <v>446</v>
-      </c>
-      <c r="D146" t="s">
-        <v>452</v>
+        <v>455</v>
+      </c>
+      <c r="D146" t="b">
+        <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F146" t="s">
         <v>13</v>
@@ -7082,16 +5738,16 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C147" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="D147" t="b">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F147" t="s">
         <v>13</v>
@@ -7102,16 +5758,16 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s">
-        <v>456</v>
-      </c>
-      <c r="D148" t="s">
-        <v>457</v>
+        <v>461</v>
+      </c>
+      <c r="D148" t="b">
+        <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F148" t="s">
         <v>13</v>
@@ -7122,16 +5778,16 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C149" t="s">
-        <v>456</v>
-      </c>
-      <c r="D149" t="s">
-        <v>460</v>
+        <v>464</v>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F149" t="s">
         <v>13</v>
@@ -7142,16 +5798,16 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C150" t="s">
-        <v>463</v>
-      </c>
-      <c r="D150" t="s">
-        <v>464</v>
+        <v>467</v>
+      </c>
+      <c r="D150" t="b">
+        <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F150" t="s">
         <v>13</v>
@@ -7162,16 +5818,16 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>463</v>
-      </c>
-      <c r="D151" t="s">
-        <v>467</v>
+        <v>470</v>
+      </c>
+      <c r="D151" t="b">
+        <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F151" t="s">
         <v>13</v>
@@ -7182,16 +5838,16 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C152" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D152" t="b">
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F152" t="s">
         <v>13</v>
@@ -7202,16 +5858,16 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C153" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D153" t="b">
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F153" t="s">
         <v>13</v>
@@ -7222,16 +5878,16 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C154" t="s">
-        <v>476</v>
-      </c>
-      <c r="D154" t="s">
-        <v>477</v>
+        <v>479</v>
+      </c>
+      <c r="D154" t="b">
+        <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F154" t="s">
         <v>13</v>
@@ -7242,16 +5898,16 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C155" t="s">
-        <v>476</v>
-      </c>
-      <c r="D155" t="s">
-        <v>480</v>
+        <v>482</v>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F155" t="s">
         <v>13</v>
@@ -7262,16 +5918,16 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C156" t="s">
-        <v>483</v>
-      </c>
-      <c r="D156" t="s">
-        <v>484</v>
+        <v>485</v>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F156" t="s">
         <v>13</v>
@@ -7282,16 +5938,16 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C157" t="s">
-        <v>483</v>
-      </c>
-      <c r="D157" t="s">
-        <v>487</v>
+        <v>488</v>
+      </c>
+      <c r="D157" t="b">
+        <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F157" t="s">
         <v>13</v>
@@ -7302,16 +5958,16 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C158" t="s">
-        <v>490</v>
-      </c>
-      <c r="D158" t="s">
+        <v>188</v>
+      </c>
+      <c r="D158" t="b">
+        <v>1</v>
+      </c>
+      <c r="E158" t="s">
         <v>491</v>
-      </c>
-      <c r="E158" t="s">
-        <v>492</v>
       </c>
       <c r="F158" t="s">
         <v>13</v>
@@ -7322,16 +5978,16 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
+        <v>492</v>
+      </c>
+      <c r="C159" t="s">
         <v>493</v>
       </c>
-      <c r="C159" t="s">
-        <v>490</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="D159" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" t="s">
         <v>494</v>
-      </c>
-      <c r="E159" t="s">
-        <v>495</v>
       </c>
       <c r="F159" t="s">
         <v>13</v>
@@ -7342,16 +5998,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
+        <v>495</v>
+      </c>
+      <c r="C160" t="s">
         <v>496</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160" t="s">
         <v>497</v>
-      </c>
-      <c r="D160" t="s">
-        <v>498</v>
-      </c>
-      <c r="E160" t="s">
-        <v>499</v>
       </c>
       <c r="F160" t="s">
         <v>13</v>
@@ -7362,16 +6018,16 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
+        <v>498</v>
+      </c>
+      <c r="C161" t="s">
+        <v>499</v>
+      </c>
+      <c r="D161" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" t="s">
         <v>500</v>
-      </c>
-      <c r="C161" t="s">
-        <v>501</v>
-      </c>
-      <c r="D161" t="s">
-        <v>502</v>
-      </c>
-      <c r="E161" t="s">
-        <v>503</v>
       </c>
       <c r="F161" t="s">
         <v>13</v>
@@ -7382,16 +6038,16 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C162" t="s">
-        <v>505</v>
-      </c>
-      <c r="D162" t="s">
         <v>502</v>
       </c>
+      <c r="D162" t="b">
+        <v>1</v>
+      </c>
       <c r="E162" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F162" t="s">
         <v>13</v>
@@ -7402,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C163" t="s">
-        <v>508</v>
-      </c>
-      <c r="D163" t="s">
-        <v>509</v>
+        <v>505</v>
+      </c>
+      <c r="D163" t="b">
+        <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F163" t="s">
         <v>13</v>
@@ -7422,16 +6078,16 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C164" t="s">
         <v>508</v>
       </c>
-      <c r="D164" t="s">
-        <v>512</v>
+      <c r="D164" t="b">
+        <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F164" t="s">
         <v>13</v>
@@ -7442,16 +6098,16 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C165" t="s">
-        <v>515</v>
-      </c>
-      <c r="D165" t="s">
-        <v>516</v>
+        <v>511</v>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F165" t="s">
         <v>13</v>
@@ -7462,16 +6118,16 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C166" t="s">
+        <v>514</v>
+      </c>
+      <c r="D166" t="b">
+        <v>1</v>
+      </c>
+      <c r="E166" t="s">
         <v>515</v>
-      </c>
-      <c r="D166" t="s">
-        <v>519</v>
-      </c>
-      <c r="E166" t="s">
-        <v>520</v>
       </c>
       <c r="F166" t="s">
         <v>13</v>
@@ -7482,16 +6138,16 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C167" t="s">
-        <v>522</v>
-      </c>
-      <c r="D167" t="s">
-        <v>523</v>
+        <v>517</v>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F167" t="s">
         <v>13</v>
@@ -7502,16 +6158,16 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C168" t="s">
-        <v>522</v>
-      </c>
-      <c r="D168" t="s">
-        <v>526</v>
+        <v>520</v>
+      </c>
+      <c r="D168" t="b">
+        <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F168" t="s">
         <v>13</v>
@@ -7522,13 +6178,13 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C169" t="s">
-        <v>522</v>
-      </c>
-      <c r="D169" t="s">
-        <v>528</v>
+        <v>523</v>
+      </c>
+      <c r="D169" t="b">
+        <v>1</v>
       </c>
       <c r="E169" t="s">
         <v>524</v>
@@ -7542,16 +6198,16 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F170" t="s">
         <v>13</v>
@@ -7562,16 +6218,16 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C171" t="s">
-        <v>532</v>
-      </c>
-      <c r="D171" t="s">
-        <v>533</v>
+        <v>529</v>
+      </c>
+      <c r="D171" t="b">
+        <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F171" t="s">
         <v>13</v>
@@ -7582,16 +6238,16 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C172" t="s">
         <v>532</v>
       </c>
-      <c r="D172" t="s">
-        <v>536</v>
+      <c r="D172" t="b">
+        <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F172" t="s">
         <v>13</v>
@@ -7602,16 +6258,16 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C173" t="s">
-        <v>539</v>
-      </c>
-      <c r="D173" t="s">
-        <v>540</v>
+        <v>535</v>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -7622,16 +6278,16 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C174" t="s">
+        <v>538</v>
+      </c>
+      <c r="D174" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
         <v>539</v>
-      </c>
-      <c r="D174" t="s">
-        <v>543</v>
-      </c>
-      <c r="E174" t="s">
-        <v>544</v>
       </c>
       <c r="F174" t="s">
         <v>13</v>
@@ -7642,16 +6298,16 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C175" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="D175" t="b">
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
@@ -7662,16 +6318,16 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C176" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D176" t="b">
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F176" t="s">
         <v>13</v>
@@ -7682,16 +6338,16 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C177" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D177" t="b">
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F177" t="s">
         <v>13</v>
@@ -7702,16 +6358,16 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C178" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D178" t="b">
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F178" t="s">
         <v>13</v>
@@ -7722,16 +6378,16 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C179" t="s">
-        <v>556</v>
+        <v>244</v>
       </c>
       <c r="D179" t="b">
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F179" t="s">
         <v>13</v>
@@ -7742,16 +6398,16 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C180" t="s">
-        <v>559</v>
-      </c>
-      <c r="D180" t="s">
-        <v>560</v>
+        <v>555</v>
+      </c>
+      <c r="D180" t="b">
+        <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F180" t="s">
         <v>13</v>
@@ -7762,16 +6418,16 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C181" t="s">
-        <v>563</v>
-      </c>
-      <c r="D181" t="s">
-        <v>564</v>
+        <v>558</v>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
       </c>
       <c r="E181" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="F181" t="s">
         <v>13</v>
@@ -7782,16 +6438,16 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C182" t="s">
-        <v>567</v>
-      </c>
-      <c r="D182" t="s">
-        <v>568</v>
+        <v>561</v>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="F182" t="s">
         <v>13</v>
@@ -7802,16 +6458,16 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="C183" t="s">
-        <v>571</v>
-      </c>
-      <c r="D183" t="s">
-        <v>572</v>
+        <v>564</v>
+      </c>
+      <c r="D183" t="b">
+        <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F183" t="s">
         <v>13</v>
@@ -7822,16 +6478,16 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C184" t="s">
-        <v>575</v>
-      </c>
-      <c r="D184" t="s">
-        <v>573</v>
+        <v>567</v>
+      </c>
+      <c r="D184" t="b">
+        <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F184" t="s">
         <v>13</v>
@@ -7842,16 +6498,16 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C185" t="s">
-        <v>578</v>
-      </c>
-      <c r="D185" t="s">
-        <v>579</v>
+        <v>570</v>
+      </c>
+      <c r="D185" t="b">
+        <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="F185" t="s">
         <v>13</v>
@@ -7862,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="C186" t="s">
-        <v>578</v>
-      </c>
-      <c r="D186" t="s">
-        <v>582</v>
+        <v>573</v>
+      </c>
+      <c r="D186" t="b">
+        <v>1</v>
       </c>
       <c r="E186" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="F186" t="s">
         <v>13</v>
@@ -7882,16 +6538,16 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C187" t="s">
-        <v>585</v>
-      </c>
-      <c r="D187" t="s">
-        <v>586</v>
+        <v>576</v>
+      </c>
+      <c r="D187" t="b">
+        <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="F187" t="s">
         <v>13</v>
@@ -7902,16 +6558,16 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C188" t="s">
-        <v>585</v>
-      </c>
-      <c r="D188" t="s">
-        <v>589</v>
+        <v>579</v>
+      </c>
+      <c r="D188" t="b">
+        <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
@@ -7922,16 +6578,16 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C189" t="s">
-        <v>592</v>
-      </c>
-      <c r="D189" t="s">
-        <v>593</v>
+        <v>582</v>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="F189" t="s">
         <v>13</v>
@@ -7942,16 +6598,16 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C190" t="s">
-        <v>592</v>
-      </c>
-      <c r="D190" t="s">
-        <v>596</v>
+        <v>585</v>
+      </c>
+      <c r="D190" t="b">
+        <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -7962,16 +6618,16 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>598</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D191" t="s">
-        <v>600</v>
+        <v>587</v>
+      </c>
+      <c r="C191" t="s">
+        <v>588</v>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="F191" t="s">
         <v>13</v>
@@ -7982,16 +6638,16 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>602</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>599</v>
+        <v>590</v>
+      </c>
+      <c r="C192" t="s">
+        <v>591</v>
       </c>
       <c r="D192" t="b">
         <v>1</v>
       </c>
       <c r="E192" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="F192" t="s">
         <v>13</v>
@@ -8002,16 +6658,16 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>604</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D193" t="s">
-        <v>601</v>
+        <v>593</v>
+      </c>
+      <c r="C193" t="s">
+        <v>594</v>
+      </c>
+      <c r="D193" t="b">
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F193" t="s">
         <v>13</v>
@@ -8022,16 +6678,16 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C194" t="s">
-        <v>608</v>
-      </c>
-      <c r="D194" t="s">
-        <v>609</v>
+        <v>246</v>
+      </c>
+      <c r="D194" t="b">
+        <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="F194" t="s">
         <v>13</v>
@@ -8042,16 +6698,16 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C195" t="s">
-        <v>608</v>
-      </c>
-      <c r="D195" t="s">
-        <v>612</v>
+        <v>599</v>
+      </c>
+      <c r="D195" t="b">
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -8062,16 +6718,16 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C196" t="s">
-        <v>615</v>
-      </c>
-      <c r="D196" t="s">
-        <v>616</v>
+        <v>602</v>
+      </c>
+      <c r="D196" t="b">
+        <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="F196" t="s">
         <v>13</v>
@@ -8082,16 +6738,16 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C197" t="s">
-        <v>615</v>
-      </c>
-      <c r="D197" t="s">
-        <v>619</v>
+        <v>605</v>
+      </c>
+      <c r="D197" t="b">
+        <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F197" t="s">
         <v>13</v>
@@ -8102,16 +6758,16 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="C198" t="s">
-        <v>622</v>
-      </c>
-      <c r="D198" t="s">
-        <v>623</v>
+        <v>608</v>
+      </c>
+      <c r="D198" t="b">
+        <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -8122,16 +6778,16 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="C199" t="s">
-        <v>626</v>
-      </c>
-      <c r="D199" t="s">
-        <v>627</v>
+        <v>611</v>
+      </c>
+      <c r="D199" t="b">
+        <v>1</v>
       </c>
       <c r="E199" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="F199" t="s">
         <v>13</v>
@@ -8142,16 +6798,16 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="C200" t="s">
-        <v>630</v>
-      </c>
-      <c r="D200" t="s">
-        <v>631</v>
+        <v>614</v>
+      </c>
+      <c r="D200" t="b">
+        <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="F200" t="s">
         <v>13</v>
@@ -8162,16 +6818,16 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="C201" t="s">
-        <v>630</v>
-      </c>
-      <c r="D201" t="s">
-        <v>634</v>
+        <v>262</v>
+      </c>
+      <c r="D201" t="b">
+        <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="F201" t="s">
         <v>13</v>
@@ -8182,16 +6838,16 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="C202" t="s">
-        <v>630</v>
-      </c>
-      <c r="D202" t="s">
-        <v>636</v>
+        <v>619</v>
+      </c>
+      <c r="D202" t="b">
+        <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="F202" t="s">
         <v>13</v>
@@ -8202,16 +6858,16 @@
         <v>8</v>
       </c>
       <c r="B203" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="C203" t="s">
-        <v>630</v>
-      </c>
-      <c r="D203" t="s">
-        <v>638</v>
+        <v>622</v>
+      </c>
+      <c r="D203" t="b">
+        <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="F203" t="s">
         <v>13</v>
@@ -8222,16 +6878,16 @@
         <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="C204" t="s">
-        <v>630</v>
-      </c>
-      <c r="D204" t="s">
-        <v>641</v>
+        <v>625</v>
+      </c>
+      <c r="D204" t="b">
+        <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -8242,16 +6898,16 @@
         <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="C205" t="s">
-        <v>630</v>
-      </c>
-      <c r="D205" t="s">
-        <v>643</v>
+        <v>304</v>
+      </c>
+      <c r="D205" t="b">
+        <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="F205" t="s">
         <v>13</v>
@@ -8262,16 +6918,16 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="C206" t="s">
-        <v>645</v>
-      </c>
-      <c r="D206" t="s">
-        <v>646</v>
+        <v>630</v>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -8282,16 +6938,16 @@
         <v>8</v>
       </c>
       <c r="B207" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="C207" t="s">
-        <v>649</v>
-      </c>
-      <c r="D207" t="s">
-        <v>560</v>
+        <v>633</v>
+      </c>
+      <c r="D207" t="b">
+        <v>1</v>
       </c>
       <c r="E207" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="F207" t="s">
         <v>13</v>
@@ -8302,16 +6958,16 @@
         <v>8</v>
       </c>
       <c r="B208" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C208" t="s">
-        <v>649</v>
-      </c>
-      <c r="D208" t="s">
-        <v>652</v>
+        <v>636</v>
+      </c>
+      <c r="D208" t="b">
+        <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="F208" t="s">
         <v>13</v>
@@ -8322,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="C209" t="s">
-        <v>655</v>
-      </c>
-      <c r="D209" t="s">
-        <v>656</v>
+        <v>639</v>
+      </c>
+      <c r="D209" t="b">
+        <v>1</v>
       </c>
       <c r="E209" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="F209" t="s">
         <v>13</v>
@@ -8342,16 +6998,16 @@
         <v>8</v>
       </c>
       <c r="B210" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="C210" t="s">
-        <v>659</v>
-      </c>
-      <c r="D210" t="s">
-        <v>657</v>
+        <v>642</v>
+      </c>
+      <c r="D210" t="b">
+        <v>1</v>
       </c>
       <c r="E210" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="F210" t="s">
         <v>13</v>
@@ -8362,16 +7018,16 @@
         <v>8</v>
       </c>
       <c r="B211" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="C211" t="s">
-        <v>659</v>
-      </c>
-      <c r="D211" t="s">
-        <v>657</v>
+        <v>645</v>
+      </c>
+      <c r="D211" t="b">
+        <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="F211" t="s">
         <v>13</v>
@@ -8382,16 +7038,16 @@
         <v>8</v>
       </c>
       <c r="B212" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="C212" t="s">
-        <v>664</v>
-      </c>
-      <c r="D212" t="s">
-        <v>665</v>
+        <v>648</v>
+      </c>
+      <c r="D212" t="b">
+        <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -8402,16 +7058,16 @@
         <v>8</v>
       </c>
       <c r="B213" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="C213" t="s">
-        <v>664</v>
-      </c>
-      <c r="D213" t="s">
-        <v>668</v>
+        <v>651</v>
+      </c>
+      <c r="D213" t="b">
+        <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="F213" t="s">
         <v>13</v>
@@ -8422,16 +7078,16 @@
         <v>8</v>
       </c>
       <c r="B214" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="C214" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="D214" t="b">
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="F214" t="s">
         <v>13</v>
@@ -8442,16 +7098,16 @@
         <v>8</v>
       </c>
       <c r="B215" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="C215" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="D215" t="b">
         <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F215" t="s">
         <v>13</v>
@@ -8462,19 +7118,19 @@
         <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="C216" t="s">
-        <v>676</v>
-      </c>
-      <c r="D216" t="s">
-        <v>677</v>
+        <v>660</v>
+      </c>
+      <c r="D216" t="b">
+        <v>1</v>
       </c>
       <c r="E216" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="F216" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8482,19 +7138,19 @@
         <v>8</v>
       </c>
       <c r="B217" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="C217" t="s">
-        <v>680</v>
-      </c>
-      <c r="D217" t="s">
-        <v>677</v>
+        <v>663</v>
+      </c>
+      <c r="D217" t="b">
+        <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="F217" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8502,19 +7158,19 @@
         <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="C218" t="s">
-        <v>683</v>
-      </c>
-      <c r="D218" t="s">
-        <v>677</v>
+        <v>666</v>
+      </c>
+      <c r="D218" t="b">
+        <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="F218" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8522,16 +7178,16 @@
         <v>8</v>
       </c>
       <c r="B219" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="C219" t="s">
-        <v>686</v>
-      </c>
-      <c r="D219" t="s">
-        <v>687</v>
+        <v>669</v>
+      </c>
+      <c r="D219" t="b">
+        <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="F219" t="s">
         <v>13</v>
@@ -8542,16 +7198,16 @@
         <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="C220" t="s">
-        <v>686</v>
-      </c>
-      <c r="D220" t="s">
-        <v>690</v>
+        <v>672</v>
+      </c>
+      <c r="D220" t="b">
+        <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="F220" t="s">
         <v>13</v>
@@ -8562,16 +7218,16 @@
         <v>8</v>
       </c>
       <c r="B221" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="C221" t="s">
-        <v>693</v>
-      </c>
-      <c r="D221" t="s">
-        <v>694</v>
+        <v>675</v>
+      </c>
+      <c r="D221" t="b">
+        <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="F221" t="s">
         <v>13</v>
@@ -8582,16 +7238,16 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="C222" t="s">
-        <v>697</v>
-      </c>
-      <c r="D222" t="s">
-        <v>698</v>
+        <v>678</v>
+      </c>
+      <c r="D222" t="b">
+        <v>1</v>
       </c>
       <c r="E222" t="s">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="F222" t="s">
         <v>13</v>
@@ -8602,16 +7258,16 @@
         <v>8</v>
       </c>
       <c r="B223" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="C223" t="s">
-        <v>697</v>
-      </c>
-      <c r="D223" t="s">
-        <v>701</v>
+        <v>681</v>
+      </c>
+      <c r="D223" t="b">
+        <v>1</v>
       </c>
       <c r="E223" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="F223" t="s">
         <v>13</v>
@@ -8622,16 +7278,16 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="C224" t="s">
-        <v>697</v>
-      </c>
-      <c r="D224" t="s">
-        <v>703</v>
+        <v>684</v>
+      </c>
+      <c r="D224" t="b">
+        <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="F224" t="s">
         <v>13</v>
@@ -8642,16 +7298,16 @@
         <v>8</v>
       </c>
       <c r="B225" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="C225" t="s">
-        <v>705</v>
-      </c>
-      <c r="D225" t="s">
-        <v>706</v>
+        <v>687</v>
+      </c>
+      <c r="D225" t="b">
+        <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="F225" t="s">
         <v>13</v>
@@ -8662,16 +7318,16 @@
         <v>8</v>
       </c>
       <c r="B226" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="C226" t="s">
-        <v>705</v>
-      </c>
-      <c r="D226" t="s">
-        <v>709</v>
+        <v>394</v>
+      </c>
+      <c r="D226" t="b">
+        <v>1</v>
       </c>
       <c r="E226" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="F226" t="s">
         <v>13</v>
@@ -8682,16 +7338,16 @@
         <v>8</v>
       </c>
       <c r="B227" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="C227" t="s">
-        <v>705</v>
-      </c>
-      <c r="D227" t="s">
-        <v>706</v>
+        <v>692</v>
+      </c>
+      <c r="D227" t="b">
+        <v>1</v>
       </c>
       <c r="E227" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="F227" t="s">
         <v>13</v>
@@ -8702,16 +7358,16 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="C228" t="s">
-        <v>714</v>
-      </c>
-      <c r="D228" t="s">
-        <v>715</v>
+        <v>402</v>
+      </c>
+      <c r="D228" t="b">
+        <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="F228" t="s">
         <v>13</v>
@@ -8722,16 +7378,16 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="C229" t="s">
-        <v>714</v>
-      </c>
-      <c r="D229" t="s">
-        <v>718</v>
+        <v>697</v>
+      </c>
+      <c r="D229" t="b">
+        <v>1</v>
       </c>
       <c r="E229" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F229" t="s">
         <v>13</v>
@@ -8742,16 +7398,16 @@
         <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="C230" t="s">
-        <v>721</v>
-      </c>
-      <c r="D230" t="s">
-        <v>722</v>
+        <v>406</v>
+      </c>
+      <c r="D230" t="b">
+        <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>723</v>
+        <v>700</v>
       </c>
       <c r="F230" t="s">
         <v>13</v>
@@ -8762,16 +7418,16 @@
         <v>8</v>
       </c>
       <c r="B231" t="s">
-        <v>724</v>
+        <v>701</v>
       </c>
       <c r="C231" t="s">
-        <v>721</v>
-      </c>
-      <c r="D231" t="s">
-        <v>725</v>
+        <v>702</v>
+      </c>
+      <c r="D231" t="b">
+        <v>1</v>
       </c>
       <c r="E231" t="s">
-        <v>726</v>
+        <v>703</v>
       </c>
       <c r="F231" t="s">
         <v>13</v>
@@ -8782,16 +7438,16 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>727</v>
+        <v>704</v>
       </c>
       <c r="C232" t="s">
-        <v>728</v>
-      </c>
-      <c r="D232" t="s">
-        <v>722</v>
+        <v>410</v>
+      </c>
+      <c r="D232" t="b">
+        <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>729</v>
+        <v>705</v>
       </c>
       <c r="F232" t="s">
         <v>13</v>
@@ -8802,16 +7458,16 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>730</v>
+        <v>706</v>
       </c>
       <c r="C233" t="s">
-        <v>728</v>
-      </c>
-      <c r="D233" t="s">
-        <v>725</v>
+        <v>707</v>
+      </c>
+      <c r="D233" t="b">
+        <v>1</v>
       </c>
       <c r="E233" t="s">
-        <v>731</v>
+        <v>708</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -8822,16 +7478,16 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>732</v>
+        <v>709</v>
       </c>
       <c r="C234" t="s">
-        <v>733</v>
-      </c>
-      <c r="D234" t="s">
-        <v>734</v>
+        <v>414</v>
+      </c>
+      <c r="D234" t="b">
+        <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -8842,16 +7498,16 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="C235" t="s">
-        <v>733</v>
-      </c>
-      <c r="D235" t="s">
-        <v>737</v>
+        <v>712</v>
+      </c>
+      <c r="D235" t="b">
+        <v>1</v>
       </c>
       <c r="E235" t="s">
-        <v>738</v>
+        <v>713</v>
       </c>
       <c r="F235" t="s">
         <v>13</v>
@@ -8862,16 +7518,16 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>739</v>
+        <v>714</v>
       </c>
       <c r="C236" t="s">
-        <v>740</v>
-      </c>
-      <c r="D236" t="s">
-        <v>723</v>
+        <v>418</v>
+      </c>
+      <c r="D236" t="b">
+        <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="F236" t="s">
         <v>13</v>
@@ -8882,16 +7538,16 @@
         <v>8</v>
       </c>
       <c r="B237" t="s">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="C237" t="s">
-        <v>742</v>
-      </c>
-      <c r="D237" t="s">
-        <v>729</v>
+        <v>717</v>
+      </c>
+      <c r="D237" t="b">
+        <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -8902,16 +7558,16 @@
         <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="C238" t="s">
-        <v>744</v>
-      </c>
-      <c r="D238" t="s">
-        <v>735</v>
+        <v>720</v>
+      </c>
+      <c r="D238" t="b">
+        <v>1</v>
       </c>
       <c r="E238" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="F238" t="s">
         <v>13</v>
@@ -8922,16 +7578,16 @@
         <v>8</v>
       </c>
       <c r="B239" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="C239" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D239" t="b">
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>747</v>
+        <v>724</v>
       </c>
       <c r="F239" t="s">
         <v>13</v>
@@ -8942,16 +7598,16 @@
         <v>8</v>
       </c>
       <c r="B240" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
       <c r="C240" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="D240" t="b">
         <v>1</v>
       </c>
       <c r="E240" t="s">
-        <v>750</v>
+        <v>727</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -8962,16 +7618,16 @@
         <v>8</v>
       </c>
       <c r="B241" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="C241" t="s">
-        <v>752</v>
+        <v>729</v>
       </c>
       <c r="D241" t="b">
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
       <c r="F241" t="s">
         <v>13</v>
@@ -8982,16 +7638,16 @@
         <v>8</v>
       </c>
       <c r="B242" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="C242" t="s">
-        <v>755</v>
-      </c>
-      <c r="D242" t="s">
-        <v>756</v>
+        <v>732</v>
+      </c>
+      <c r="D242" t="b">
+        <v>1</v>
       </c>
       <c r="E242" t="s">
-        <v>757</v>
+        <v>733</v>
       </c>
       <c r="F242" t="s">
         <v>13</v>
@@ -9002,16 +7658,16 @@
         <v>8</v>
       </c>
       <c r="B243" t="s">
-        <v>758</v>
+        <v>734</v>
       </c>
       <c r="C243" t="s">
-        <v>755</v>
-      </c>
-      <c r="D243" t="s">
-        <v>759</v>
+        <v>735</v>
+      </c>
+      <c r="D243" t="b">
+        <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="F243" t="s">
         <v>13</v>
@@ -9022,16 +7678,16 @@
         <v>8</v>
       </c>
       <c r="B244" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="C244" t="s">
-        <v>762</v>
-      </c>
-      <c r="D244" t="s">
-        <v>763</v>
+        <v>50</v>
+      </c>
+      <c r="D244" t="b">
+        <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>764</v>
+        <v>738</v>
       </c>
       <c r="F244" t="s">
         <v>13</v>
@@ -9042,16 +7698,16 @@
         <v>8</v>
       </c>
       <c r="B245" t="s">
-        <v>765</v>
+        <v>739</v>
       </c>
       <c r="C245" t="s">
-        <v>766</v>
-      </c>
-      <c r="D245" t="s">
-        <v>767</v>
+        <v>740</v>
+      </c>
+      <c r="D245" t="b">
+        <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>768</v>
+        <v>741</v>
       </c>
       <c r="F245" t="s">
         <v>13</v>
@@ -9062,16 +7718,16 @@
         <v>8</v>
       </c>
       <c r="B246" t="s">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="C246" t="s">
-        <v>766</v>
-      </c>
-      <c r="D246" t="s">
-        <v>770</v>
+        <v>743</v>
+      </c>
+      <c r="D246" t="b">
+        <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="F246" t="s">
         <v>13</v>
@@ -9082,16 +7738,16 @@
         <v>8</v>
       </c>
       <c r="B247" t="s">
-        <v>772</v>
+        <v>745</v>
       </c>
       <c r="C247" t="s">
-        <v>773</v>
-      </c>
-      <c r="D247" t="s">
-        <v>774</v>
+        <v>746</v>
+      </c>
+      <c r="D247" t="b">
+        <v>1</v>
       </c>
       <c r="E247" t="s">
-        <v>775</v>
+        <v>747</v>
       </c>
       <c r="F247" t="s">
         <v>13</v>
@@ -9102,16 +7758,16 @@
         <v>8</v>
       </c>
       <c r="B248" t="s">
-        <v>776</v>
-      </c>
-      <c r="C248" t="s">
-        <v>773</v>
-      </c>
-      <c r="D248" t="s">
-        <v>777</v>
-      </c>
-      <c r="E248" t="s">
-        <v>775</v>
+        <v>748</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="D248" t="b">
+        <v>1</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>750</v>
       </c>
       <c r="F248" t="s">
         <v>13</v>
@@ -9122,16 +7778,16 @@
         <v>8</v>
       </c>
       <c r="B249" t="s">
-        <v>778</v>
-      </c>
-      <c r="C249" t="s">
-        <v>773</v>
-      </c>
-      <c r="D249" t="s">
-        <v>779</v>
-      </c>
-      <c r="E249" t="s">
-        <v>775</v>
+        <v>751</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D249" t="b">
+        <v>1</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>753</v>
       </c>
       <c r="F249" t="s">
         <v>13</v>
@@ -9142,2857 +7798,57 @@
         <v>8</v>
       </c>
       <c r="B250" t="s">
-        <v>780</v>
-      </c>
-      <c r="C250" t="s">
-        <v>781</v>
-      </c>
-      <c r="D250" t="s">
-        <v>782</v>
-      </c>
-      <c r="E250" t="s">
-        <v>783</v>
+        <v>754</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D250" t="b">
+        <v>1</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>756</v>
       </c>
       <c r="F250" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>8</v>
-      </c>
-      <c r="B251" t="s">
-        <v>784</v>
-      </c>
-      <c r="C251" t="s">
-        <v>781</v>
-      </c>
-      <c r="D251" t="s">
-        <v>785</v>
-      </c>
-      <c r="E251" t="s">
-        <v>783</v>
-      </c>
-      <c r="F251" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>8</v>
-      </c>
-      <c r="B252" t="s">
-        <v>786</v>
-      </c>
-      <c r="C252" t="s">
-        <v>787</v>
-      </c>
-      <c r="D252" t="s">
-        <v>788</v>
-      </c>
-      <c r="E252" t="s">
-        <v>789</v>
-      </c>
-      <c r="F252" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>8</v>
-      </c>
-      <c r="B253" t="s">
-        <v>790</v>
-      </c>
-      <c r="C253" t="s">
-        <v>787</v>
-      </c>
-      <c r="D253" t="s">
-        <v>791</v>
-      </c>
-      <c r="E253" t="s">
-        <v>792</v>
-      </c>
-      <c r="F253" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>8</v>
-      </c>
-      <c r="B254" t="s">
-        <v>793</v>
-      </c>
-      <c r="C254" t="s">
-        <v>794</v>
-      </c>
-      <c r="D254" t="s">
-        <v>795</v>
-      </c>
-      <c r="E254" t="s">
-        <v>796</v>
-      </c>
-      <c r="F254" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>8</v>
-      </c>
-      <c r="B255" t="s">
-        <v>797</v>
-      </c>
-      <c r="C255" t="s">
-        <v>798</v>
-      </c>
-      <c r="D255" t="s">
-        <v>799</v>
-      </c>
-      <c r="E255" t="s">
-        <v>800</v>
-      </c>
-      <c r="F255" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>8</v>
-      </c>
-      <c r="B256" t="s">
-        <v>801</v>
-      </c>
-      <c r="C256" t="s">
-        <v>798</v>
-      </c>
-      <c r="D256" t="s">
-        <v>802</v>
-      </c>
-      <c r="E256" t="s">
-        <v>803</v>
-      </c>
-      <c r="F256" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>8</v>
-      </c>
-      <c r="B257" t="s">
-        <v>804</v>
-      </c>
-      <c r="C257" t="s">
-        <v>805</v>
-      </c>
-      <c r="D257" t="s">
-        <v>806</v>
-      </c>
-      <c r="E257" t="s">
-        <v>807</v>
-      </c>
-      <c r="F257" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>8</v>
-      </c>
-      <c r="B258" t="s">
-        <v>808</v>
-      </c>
-      <c r="C258" t="s">
-        <v>805</v>
-      </c>
-      <c r="D258" t="s">
-        <v>809</v>
-      </c>
-      <c r="E258" t="s">
-        <v>810</v>
-      </c>
-      <c r="F258" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>8</v>
-      </c>
-      <c r="B259" t="s">
-        <v>811</v>
-      </c>
-      <c r="C259" t="s">
-        <v>812</v>
-      </c>
-      <c r="D259" t="s">
-        <v>813</v>
-      </c>
-      <c r="E259" t="s">
-        <v>814</v>
-      </c>
-      <c r="F259" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>8</v>
-      </c>
-      <c r="B260" t="s">
-        <v>815</v>
-      </c>
-      <c r="C260" t="s">
-        <v>816</v>
-      </c>
-      <c r="D260" t="s">
-        <v>817</v>
-      </c>
-      <c r="E260" t="s">
-        <v>818</v>
-      </c>
-      <c r="F260" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>8</v>
-      </c>
-      <c r="B261" t="s">
-        <v>819</v>
-      </c>
-      <c r="C261" t="s">
-        <v>816</v>
-      </c>
-      <c r="D261" t="s">
-        <v>820</v>
-      </c>
-      <c r="E261" t="s">
-        <v>821</v>
-      </c>
-      <c r="F261" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>8</v>
-      </c>
-      <c r="B262" t="s">
-        <v>822</v>
-      </c>
-      <c r="C262" t="s">
-        <v>823</v>
-      </c>
-      <c r="D262" t="s">
-        <v>824</v>
-      </c>
-      <c r="E262" t="s">
-        <v>825</v>
-      </c>
-      <c r="F262" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>8</v>
-      </c>
-      <c r="B263" t="s">
-        <v>826</v>
-      </c>
-      <c r="C263" t="s">
-        <v>823</v>
-      </c>
-      <c r="D263" t="s">
-        <v>827</v>
-      </c>
-      <c r="E263" t="s">
-        <v>828</v>
-      </c>
-      <c r="F263" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>8</v>
-      </c>
-      <c r="B264" t="s">
-        <v>829</v>
-      </c>
-      <c r="C264" t="s">
-        <v>830</v>
-      </c>
-      <c r="D264" t="s">
-        <v>831</v>
-      </c>
-      <c r="E264" t="s">
-        <v>832</v>
-      </c>
-      <c r="F264" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>8</v>
-      </c>
-      <c r="B265" t="s">
-        <v>833</v>
-      </c>
-      <c r="C265" t="s">
-        <v>834</v>
-      </c>
-      <c r="D265" t="s">
-        <v>835</v>
-      </c>
-      <c r="E265" t="s">
-        <v>836</v>
-      </c>
-      <c r="F265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>8</v>
-      </c>
-      <c r="B266" t="s">
-        <v>837</v>
-      </c>
-      <c r="C266" t="s">
-        <v>834</v>
-      </c>
-      <c r="D266" t="s">
-        <v>838</v>
-      </c>
-      <c r="E266" t="s">
-        <v>839</v>
-      </c>
-      <c r="F266" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>8</v>
-      </c>
-      <c r="B267" t="s">
-        <v>840</v>
-      </c>
-      <c r="C267" t="s">
-        <v>841</v>
-      </c>
-      <c r="D267" t="s">
-        <v>842</v>
-      </c>
-      <c r="E267" t="s">
-        <v>843</v>
-      </c>
-      <c r="F267" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>8</v>
-      </c>
-      <c r="B268" t="s">
-        <v>844</v>
-      </c>
-      <c r="C268" t="s">
-        <v>841</v>
-      </c>
-      <c r="D268" t="s">
-        <v>845</v>
-      </c>
-      <c r="E268" t="s">
-        <v>846</v>
-      </c>
-      <c r="F268" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>8</v>
-      </c>
-      <c r="B269" t="s">
-        <v>847</v>
-      </c>
-      <c r="C269" t="s">
-        <v>848</v>
-      </c>
-      <c r="D269" t="s">
-        <v>849</v>
-      </c>
-      <c r="E269" t="s">
-        <v>850</v>
-      </c>
-      <c r="F269" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>8</v>
-      </c>
-      <c r="B270" t="s">
-        <v>851</v>
-      </c>
-      <c r="C270" t="s">
-        <v>852</v>
-      </c>
-      <c r="D270" t="s">
-        <v>853</v>
-      </c>
-      <c r="E270" t="s">
-        <v>854</v>
-      </c>
-      <c r="F270" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>8</v>
-      </c>
-      <c r="B271" t="s">
-        <v>855</v>
-      </c>
-      <c r="C271" t="s">
-        <v>852</v>
-      </c>
-      <c r="D271" t="s">
-        <v>856</v>
-      </c>
-      <c r="E271" t="s">
-        <v>857</v>
-      </c>
-      <c r="F271" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>8</v>
-      </c>
-      <c r="B272" t="s">
-        <v>858</v>
-      </c>
-      <c r="C272" t="s">
-        <v>859</v>
-      </c>
-      <c r="D272" t="s">
-        <v>860</v>
-      </c>
-      <c r="E272" t="s">
-        <v>861</v>
-      </c>
-      <c r="F272" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>8</v>
-      </c>
-      <c r="B273" t="s">
-        <v>862</v>
-      </c>
-      <c r="C273" t="s">
-        <v>859</v>
-      </c>
-      <c r="D273" t="s">
-        <v>863</v>
-      </c>
-      <c r="E273" t="s">
-        <v>864</v>
-      </c>
-      <c r="F273" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>8</v>
-      </c>
-      <c r="B274" t="s">
-        <v>865</v>
-      </c>
-      <c r="C274" t="s">
-        <v>866</v>
-      </c>
-      <c r="D274" t="s">
-        <v>867</v>
-      </c>
-      <c r="E274" t="s">
-        <v>868</v>
-      </c>
-      <c r="F274" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>8</v>
-      </c>
-      <c r="B275" t="s">
-        <v>869</v>
-      </c>
-      <c r="C275" t="s">
-        <v>870</v>
-      </c>
-      <c r="D275" t="b">
-        <v>1</v>
-      </c>
-      <c r="E275" t="s">
-        <v>871</v>
-      </c>
-      <c r="F275" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>8</v>
-      </c>
-      <c r="B276" t="s">
-        <v>872</v>
-      </c>
-      <c r="C276" t="s">
-        <v>873</v>
-      </c>
-      <c r="D276" t="b">
-        <v>1</v>
-      </c>
-      <c r="E276" t="s">
-        <v>874</v>
-      </c>
-      <c r="F276" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>8</v>
-      </c>
-      <c r="B277" t="s">
-        <v>875</v>
-      </c>
-      <c r="C277" t="s">
-        <v>876</v>
-      </c>
-      <c r="D277" t="b">
-        <v>1</v>
-      </c>
-      <c r="E277" t="s">
-        <v>877</v>
-      </c>
-      <c r="F277" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>8</v>
-      </c>
-      <c r="B278" t="s">
-        <v>878</v>
-      </c>
-      <c r="C278" t="s">
-        <v>879</v>
-      </c>
-      <c r="D278" t="b">
-        <v>1</v>
-      </c>
-      <c r="E278" t="s">
-        <v>880</v>
-      </c>
-      <c r="F278" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>8</v>
-      </c>
-      <c r="B279" t="s">
-        <v>881</v>
-      </c>
-      <c r="C279" t="s">
-        <v>882</v>
-      </c>
-      <c r="D279" t="b">
-        <v>1</v>
-      </c>
-      <c r="E279" t="s">
-        <v>883</v>
-      </c>
-      <c r="F279" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>8</v>
-      </c>
-      <c r="B280" t="s">
-        <v>884</v>
-      </c>
-      <c r="C280" t="s">
-        <v>885</v>
-      </c>
-      <c r="D280" t="b">
-        <v>1</v>
-      </c>
-      <c r="E280" t="s">
-        <v>886</v>
-      </c>
-      <c r="F280" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>8</v>
-      </c>
-      <c r="B281" t="s">
-        <v>887</v>
-      </c>
-      <c r="C281" t="s">
-        <v>888</v>
-      </c>
-      <c r="D281" t="b">
-        <v>1</v>
-      </c>
-      <c r="E281" t="s">
-        <v>889</v>
-      </c>
-      <c r="F281" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>8</v>
-      </c>
-      <c r="B282" t="s">
-        <v>890</v>
-      </c>
-      <c r="C282" t="s">
-        <v>891</v>
-      </c>
-      <c r="D282" t="b">
-        <v>1</v>
-      </c>
-      <c r="E282" t="s">
-        <v>892</v>
-      </c>
-      <c r="F282" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>8</v>
-      </c>
-      <c r="B283" t="s">
-        <v>893</v>
-      </c>
-      <c r="C283" t="s">
-        <v>894</v>
-      </c>
-      <c r="D283" t="b">
-        <v>1</v>
-      </c>
-      <c r="E283" t="s">
-        <v>895</v>
-      </c>
-      <c r="F283" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>8</v>
-      </c>
-      <c r="B284" t="s">
-        <v>896</v>
-      </c>
-      <c r="C284" t="s">
-        <v>897</v>
-      </c>
-      <c r="D284" t="b">
-        <v>1</v>
-      </c>
-      <c r="E284" t="s">
-        <v>898</v>
-      </c>
-      <c r="F284" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>8</v>
-      </c>
-      <c r="B285" t="s">
-        <v>899</v>
-      </c>
-      <c r="C285" t="s">
-        <v>900</v>
-      </c>
-      <c r="D285" t="b">
-        <v>1</v>
-      </c>
-      <c r="E285" t="s">
-        <v>901</v>
-      </c>
-      <c r="F285" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>8</v>
-      </c>
-      <c r="B286" t="s">
-        <v>902</v>
-      </c>
-      <c r="C286" t="s">
-        <v>903</v>
-      </c>
-      <c r="D286" t="b">
-        <v>1</v>
-      </c>
-      <c r="E286" t="s">
-        <v>904</v>
-      </c>
-      <c r="F286" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>8</v>
-      </c>
-      <c r="B287" t="s">
-        <v>905</v>
-      </c>
-      <c r="C287" t="s">
-        <v>906</v>
-      </c>
-      <c r="D287" t="b">
-        <v>1</v>
-      </c>
-      <c r="E287" t="s">
-        <v>907</v>
-      </c>
-      <c r="F287" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>8</v>
-      </c>
-      <c r="B288" t="s">
-        <v>908</v>
-      </c>
-      <c r="C288" t="s">
-        <v>909</v>
-      </c>
-      <c r="D288" t="b">
-        <v>1</v>
-      </c>
-      <c r="E288" t="s">
-        <v>910</v>
-      </c>
-      <c r="F288" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>8</v>
-      </c>
-      <c r="B289" t="s">
-        <v>911</v>
-      </c>
-      <c r="C289" t="s">
-        <v>912</v>
-      </c>
-      <c r="D289" t="b">
-        <v>1</v>
-      </c>
-      <c r="E289" t="s">
-        <v>913</v>
-      </c>
-      <c r="F289" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>8</v>
-      </c>
-      <c r="B290" t="s">
-        <v>914</v>
-      </c>
-      <c r="C290" t="s">
-        <v>915</v>
-      </c>
-      <c r="D290" t="b">
-        <v>1</v>
-      </c>
-      <c r="E290" t="s">
-        <v>916</v>
-      </c>
-      <c r="F290" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>8</v>
-      </c>
-      <c r="B291" t="s">
-        <v>917</v>
-      </c>
-      <c r="C291" t="s">
-        <v>918</v>
-      </c>
-      <c r="D291" t="b">
-        <v>1</v>
-      </c>
-      <c r="E291" t="s">
-        <v>919</v>
-      </c>
-      <c r="F291" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>8</v>
-      </c>
-      <c r="B292" t="s">
-        <v>920</v>
-      </c>
-      <c r="C292" t="s">
-        <v>921</v>
-      </c>
-      <c r="D292" t="b">
-        <v>1</v>
-      </c>
-      <c r="E292" t="s">
-        <v>922</v>
-      </c>
-      <c r="F292" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>8</v>
-      </c>
-      <c r="B293" t="s">
-        <v>923</v>
-      </c>
-      <c r="C293" t="s">
-        <v>924</v>
-      </c>
-      <c r="D293" t="b">
-        <v>1</v>
-      </c>
-      <c r="E293" t="s">
-        <v>925</v>
-      </c>
-      <c r="F293" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>8</v>
-      </c>
-      <c r="B294" t="s">
-        <v>926</v>
-      </c>
-      <c r="C294" t="s">
-        <v>927</v>
-      </c>
-      <c r="D294" t="b">
-        <v>1</v>
-      </c>
-      <c r="E294" t="s">
-        <v>928</v>
-      </c>
-      <c r="F294" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>8</v>
-      </c>
-      <c r="B295" t="s">
-        <v>929</v>
-      </c>
-      <c r="C295" t="s">
-        <v>930</v>
-      </c>
-      <c r="D295" t="b">
-        <v>1</v>
-      </c>
-      <c r="E295" t="s">
-        <v>931</v>
-      </c>
-      <c r="F295" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>8</v>
-      </c>
-      <c r="B296" t="s">
-        <v>932</v>
-      </c>
-      <c r="C296" t="s">
-        <v>933</v>
-      </c>
-      <c r="D296" t="b">
-        <v>1</v>
-      </c>
-      <c r="E296" t="s">
-        <v>934</v>
-      </c>
-      <c r="F296" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>8</v>
-      </c>
-      <c r="B297" t="s">
-        <v>935</v>
-      </c>
-      <c r="C297" t="s">
-        <v>936</v>
-      </c>
-      <c r="D297" t="b">
-        <v>1</v>
-      </c>
-      <c r="E297" t="s">
-        <v>937</v>
-      </c>
-      <c r="F297" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>8</v>
-      </c>
-      <c r="B298" t="s">
-        <v>938</v>
-      </c>
-      <c r="C298" t="s">
-        <v>322</v>
-      </c>
-      <c r="D298" t="b">
-        <v>1</v>
-      </c>
-      <c r="E298" t="s">
-        <v>939</v>
-      </c>
-      <c r="F298" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>8</v>
-      </c>
-      <c r="B299" t="s">
-        <v>940</v>
-      </c>
-      <c r="C299" t="s">
-        <v>941</v>
-      </c>
-      <c r="D299" t="b">
-        <v>1</v>
-      </c>
-      <c r="E299" t="s">
-        <v>942</v>
-      </c>
-      <c r="F299" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>8</v>
-      </c>
-      <c r="B300" t="s">
-        <v>943</v>
-      </c>
-      <c r="C300" t="s">
-        <v>944</v>
-      </c>
-      <c r="D300" t="b">
-        <v>1</v>
-      </c>
-      <c r="E300" t="s">
-        <v>945</v>
-      </c>
-      <c r="F300" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>8</v>
-      </c>
-      <c r="B301" t="s">
-        <v>946</v>
-      </c>
-      <c r="C301" t="s">
-        <v>947</v>
-      </c>
-      <c r="D301" t="b">
-        <v>1</v>
-      </c>
-      <c r="E301" t="s">
-        <v>948</v>
-      </c>
-      <c r="F301" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>8</v>
-      </c>
-      <c r="B302" t="s">
-        <v>949</v>
-      </c>
-      <c r="C302" t="s">
-        <v>950</v>
-      </c>
-      <c r="D302" t="b">
-        <v>1</v>
-      </c>
-      <c r="E302" t="s">
-        <v>951</v>
-      </c>
-      <c r="F302" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>8</v>
-      </c>
-      <c r="B303" t="s">
-        <v>952</v>
-      </c>
-      <c r="C303" t="s">
-        <v>953</v>
-      </c>
-      <c r="D303" t="b">
-        <v>1</v>
-      </c>
-      <c r="E303" t="s">
-        <v>954</v>
-      </c>
-      <c r="F303" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>8</v>
-      </c>
-      <c r="B304" t="s">
-        <v>955</v>
-      </c>
-      <c r="C304" t="s">
-        <v>956</v>
-      </c>
-      <c r="D304" t="b">
-        <v>1</v>
-      </c>
-      <c r="E304" t="s">
-        <v>957</v>
-      </c>
-      <c r="F304" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>8</v>
-      </c>
-      <c r="B305" t="s">
-        <v>958</v>
-      </c>
-      <c r="C305" t="s">
-        <v>959</v>
-      </c>
-      <c r="D305" t="b">
-        <v>1</v>
-      </c>
-      <c r="E305" t="s">
-        <v>960</v>
-      </c>
-      <c r="F305" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>8</v>
-      </c>
-      <c r="B306" t="s">
-        <v>961</v>
-      </c>
-      <c r="C306" t="s">
-        <v>962</v>
-      </c>
-      <c r="D306" t="b">
-        <v>1</v>
-      </c>
-      <c r="E306" t="s">
-        <v>963</v>
-      </c>
-      <c r="F306" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>8</v>
-      </c>
-      <c r="B307" t="s">
-        <v>964</v>
-      </c>
-      <c r="C307" t="s">
-        <v>965</v>
-      </c>
-      <c r="D307" t="b">
-        <v>1</v>
-      </c>
-      <c r="E307" t="s">
-        <v>966</v>
-      </c>
-      <c r="F307" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>8</v>
-      </c>
-      <c r="B308" t="s">
-        <v>967</v>
-      </c>
-      <c r="C308" t="s">
-        <v>968</v>
-      </c>
-      <c r="D308" t="b">
-        <v>1</v>
-      </c>
-      <c r="E308" t="s">
-        <v>969</v>
-      </c>
-      <c r="F308" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>8</v>
-      </c>
-      <c r="B309" t="s">
-        <v>970</v>
-      </c>
-      <c r="C309" t="s">
-        <v>971</v>
-      </c>
-      <c r="D309" t="b">
-        <v>1</v>
-      </c>
-      <c r="E309" t="s">
-        <v>972</v>
-      </c>
-      <c r="F309" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>8</v>
-      </c>
-      <c r="B310" t="s">
-        <v>973</v>
-      </c>
-      <c r="C310" t="s">
-        <v>974</v>
-      </c>
-      <c r="D310" t="b">
-        <v>1</v>
-      </c>
-      <c r="E310" t="s">
-        <v>975</v>
-      </c>
-      <c r="F310" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>8</v>
-      </c>
-      <c r="B311" t="s">
-        <v>976</v>
-      </c>
-      <c r="C311" t="s">
-        <v>977</v>
-      </c>
-      <c r="D311" t="b">
-        <v>1</v>
-      </c>
-      <c r="E311" t="s">
-        <v>978</v>
-      </c>
-      <c r="F311" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>8</v>
-      </c>
-      <c r="B312" t="s">
-        <v>979</v>
-      </c>
-      <c r="C312" t="s">
-        <v>980</v>
-      </c>
-      <c r="D312" t="b">
-        <v>1</v>
-      </c>
-      <c r="E312" t="s">
-        <v>981</v>
-      </c>
-      <c r="F312" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>8</v>
-      </c>
-      <c r="B313" t="s">
-        <v>982</v>
-      </c>
-      <c r="C313" t="s">
-        <v>983</v>
-      </c>
-      <c r="D313" t="b">
-        <v>1</v>
-      </c>
-      <c r="E313" t="s">
-        <v>984</v>
-      </c>
-      <c r="F313" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>8</v>
-      </c>
-      <c r="B314" t="s">
-        <v>985</v>
-      </c>
-      <c r="C314" t="s">
-        <v>986</v>
-      </c>
-      <c r="D314" t="b">
-        <v>1</v>
-      </c>
-      <c r="E314" t="s">
-        <v>987</v>
-      </c>
-      <c r="F314" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>8</v>
-      </c>
-      <c r="B315" t="s">
-        <v>988</v>
-      </c>
-      <c r="C315" t="s">
-        <v>989</v>
-      </c>
-      <c r="D315" t="b">
-        <v>1</v>
-      </c>
-      <c r="E315" t="s">
-        <v>990</v>
-      </c>
-      <c r="F315" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>8</v>
-      </c>
-      <c r="B316" t="s">
-        <v>991</v>
-      </c>
-      <c r="C316" t="s">
-        <v>992</v>
-      </c>
-      <c r="D316" t="b">
-        <v>1</v>
-      </c>
-      <c r="E316" t="s">
-        <v>993</v>
-      </c>
-      <c r="F316" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>8</v>
-      </c>
-      <c r="B317" t="s">
-        <v>994</v>
-      </c>
-      <c r="C317" t="s">
-        <v>995</v>
-      </c>
-      <c r="D317" t="b">
-        <v>1</v>
-      </c>
-      <c r="E317" t="s">
-        <v>996</v>
-      </c>
-      <c r="F317" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>8</v>
-      </c>
-      <c r="B318" t="s">
-        <v>997</v>
-      </c>
-      <c r="C318" t="s">
-        <v>998</v>
-      </c>
-      <c r="D318" t="b">
-        <v>1</v>
-      </c>
-      <c r="E318" t="s">
-        <v>999</v>
-      </c>
-      <c r="F318" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>8</v>
-      </c>
-      <c r="B319" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C319" t="s">
-        <v>434</v>
-      </c>
-      <c r="D319" t="b">
-        <v>1</v>
-      </c>
-      <c r="E319" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F319" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>8</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C320" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D320" t="b">
-        <v>1</v>
-      </c>
-      <c r="E320" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F320" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>8</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C321" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D321" t="b">
-        <v>1</v>
-      </c>
-      <c r="E321" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F321" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>8</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C322" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D322" t="b">
-        <v>1</v>
-      </c>
-      <c r="E322" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F322" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>8</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C323" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D323" t="b">
-        <v>1</v>
-      </c>
-      <c r="E323" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F323" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>8</v>
-      </c>
-      <c r="B324" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C324" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D324" t="b">
-        <v>1</v>
-      </c>
-      <c r="E324" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F324" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>8</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C325" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D325" t="b">
-        <v>1</v>
-      </c>
-      <c r="E325" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F325" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>8</v>
-      </c>
-      <c r="B326" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C326" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D326" t="b">
-        <v>1</v>
-      </c>
-      <c r="E326" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F326" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>8</v>
-      </c>
-      <c r="B327" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C327" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D327" t="b">
-        <v>1</v>
-      </c>
-      <c r="E327" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F327" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>8</v>
-      </c>
-      <c r="B328" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C328" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D328" t="b">
-        <v>1</v>
-      </c>
-      <c r="E328" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F328" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>8</v>
-      </c>
-      <c r="B329" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C329" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D329" t="b">
-        <v>1</v>
-      </c>
-      <c r="E329" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F329" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>8</v>
-      </c>
-      <c r="B330" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C330" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D330" t="b">
-        <v>1</v>
-      </c>
-      <c r="E330" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F330" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>8</v>
-      </c>
-      <c r="B331" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C331" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D331" t="b">
-        <v>1</v>
-      </c>
-      <c r="E331" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F331" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>8</v>
-      </c>
-      <c r="B332" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C332" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D332" t="b">
-        <v>1</v>
-      </c>
-      <c r="E332" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F332" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>8</v>
-      </c>
-      <c r="B333" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C333" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D333" t="b">
-        <v>1</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F333" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>8</v>
-      </c>
-      <c r="B334" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C334" t="s">
-        <v>446</v>
-      </c>
-      <c r="D334" t="b">
-        <v>1</v>
-      </c>
-      <c r="E334" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F334" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>8</v>
-      </c>
-      <c r="B335" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C335" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D335" t="b">
-        <v>1</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F335" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>8</v>
-      </c>
-      <c r="B336" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C336" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D336" t="b">
-        <v>1</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F336" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>8</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C337" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D337" t="b">
-        <v>1</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F337" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>8</v>
-      </c>
-      <c r="B338" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D338" t="b">
-        <v>1</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F338" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>8</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C339" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D339" t="b">
-        <v>1</v>
-      </c>
-      <c r="E339" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F339" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>8</v>
-      </c>
-      <c r="B340" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C340" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D340" t="b">
-        <v>1</v>
-      </c>
-      <c r="E340" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F340" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>8</v>
-      </c>
-      <c r="B341" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C341" t="s">
-        <v>522</v>
-      </c>
-      <c r="D341" t="b">
-        <v>1</v>
-      </c>
-      <c r="E341" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F341" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>8</v>
-      </c>
-      <c r="B342" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C342" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D342" t="b">
-        <v>1</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F342" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>8</v>
-      </c>
-      <c r="B343" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C343" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D343" t="b">
-        <v>1</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F343" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>8</v>
-      </c>
-      <c r="B344" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C344" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D344" t="b">
-        <v>1</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F344" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>8</v>
-      </c>
-      <c r="B345" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C345" t="s">
-        <v>599</v>
-      </c>
-      <c r="D345" t="b">
-        <v>1</v>
-      </c>
-      <c r="E345" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F345" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>8</v>
-      </c>
-      <c r="B346" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C346" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D346" t="b">
-        <v>1</v>
-      </c>
-      <c r="E346" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F346" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>8</v>
-      </c>
-      <c r="B347" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D347" t="b">
-        <v>1</v>
-      </c>
-      <c r="E347" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F347" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>8</v>
-      </c>
-      <c r="B348" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D348" t="b">
-        <v>1</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F348" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>8</v>
-      </c>
-      <c r="B349" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D349" t="b">
-        <v>1</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F349" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>8</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D350" t="b">
-        <v>1</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F350" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>8</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D351" t="b">
-        <v>1</v>
-      </c>
-      <c r="E351" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F351" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>8</v>
-      </c>
-      <c r="B352" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C352" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D352" t="b">
-        <v>1</v>
-      </c>
-      <c r="E352" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F352" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>8</v>
-      </c>
-      <c r="B353" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C353" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D353" t="b">
-        <v>1</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F353" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>8</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C354" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D354" t="b">
-        <v>1</v>
-      </c>
-      <c r="E354" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F354" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>8</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C355" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D355" t="b">
-        <v>1</v>
-      </c>
-      <c r="E355" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F355" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>8</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C356" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D356" t="b">
-        <v>1</v>
-      </c>
-      <c r="E356" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F356" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>8</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C357" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D357" t="b">
-        <v>1</v>
-      </c>
-      <c r="E357" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F357" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>8</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C358" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D358" t="b">
-        <v>1</v>
-      </c>
-      <c r="E358" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F358" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
-        <v>8</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C359" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D359" t="b">
-        <v>1</v>
-      </c>
-      <c r="E359" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F359" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
-        <v>8</v>
-      </c>
-      <c r="B360" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C360" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D360" t="b">
-        <v>1</v>
-      </c>
-      <c r="E360" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F360" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>8</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C361" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D361" t="b">
-        <v>1</v>
-      </c>
-      <c r="E361" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F361" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
-        <v>8</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C362" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D362" t="b">
-        <v>1</v>
-      </c>
-      <c r="E362" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F362" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
-        <v>8</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C363" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D363" t="b">
-        <v>1</v>
-      </c>
-      <c r="E363" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F363" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>8</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D364" t="b">
-        <v>1</v>
-      </c>
-      <c r="E364" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F364" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>8</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D365" t="b">
-        <v>1</v>
-      </c>
-      <c r="E365" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F365" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>8</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C366" t="s">
-        <v>773</v>
-      </c>
-      <c r="D366" t="b">
-        <v>1</v>
-      </c>
-      <c r="E366" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F366" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>8</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D367" t="b">
-        <v>1</v>
-      </c>
-      <c r="E367" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F367" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>8</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C368" t="s">
-        <v>794</v>
-      </c>
-      <c r="D368" t="b">
-        <v>1</v>
-      </c>
-      <c r="E368" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F368" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
-        <v>8</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D369" t="b">
-        <v>1</v>
-      </c>
-      <c r="E369" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F369" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
-        <v>8</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C370" t="s">
-        <v>812</v>
-      </c>
-      <c r="D370" t="b">
-        <v>1</v>
-      </c>
-      <c r="E370" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F370" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
-        <v>8</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D371" t="b">
-        <v>1</v>
-      </c>
-      <c r="E371" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F371" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
-        <v>8</v>
-      </c>
-      <c r="B372" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C372" t="s">
-        <v>830</v>
-      </c>
-      <c r="D372" t="b">
-        <v>1</v>
-      </c>
-      <c r="E372" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F372" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
-        <v>8</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D373" t="b">
-        <v>1</v>
-      </c>
-      <c r="E373" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F373" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>8</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C374" t="s">
-        <v>848</v>
-      </c>
-      <c r="D374" t="b">
-        <v>1</v>
-      </c>
-      <c r="E374" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F374" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
-        <v>8</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D375" t="b">
-        <v>1</v>
-      </c>
-      <c r="E375" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F375" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
-        <v>8</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C376" t="s">
-        <v>866</v>
-      </c>
-      <c r="D376" t="b">
-        <v>1</v>
-      </c>
-      <c r="E376" t="s">
-        <v>1163</v>
-      </c>
-      <c r="F376" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
-        <v>8</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C377" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D377" t="b">
-        <v>1</v>
-      </c>
-      <c r="E377" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F377" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
-        <v>8</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D378" t="b">
-        <v>1</v>
-      </c>
-      <c r="E378" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F378" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
-        <v>8</v>
-      </c>
-      <c r="B379" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D379" t="b">
-        <v>1</v>
-      </c>
-      <c r="E379" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F379" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
-        <v>8</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C380" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D380" t="b">
-        <v>1</v>
-      </c>
-      <c r="E380" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F380" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
-        <v>8</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D381" t="b">
-        <v>1</v>
-      </c>
-      <c r="E381" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F381" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
-        <v>8</v>
-      </c>
-      <c r="B382" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C382" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D382" t="b">
-        <v>1</v>
-      </c>
-      <c r="E382" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F382" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
-        <v>8</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C383" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D383" t="b">
-        <v>1</v>
-      </c>
-      <c r="E383" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F383" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
-        <v>8</v>
-      </c>
-      <c r="B384" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C384" t="s">
-        <v>164</v>
-      </c>
-      <c r="D384" t="b">
-        <v>1</v>
-      </c>
-      <c r="E384" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F384" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>8</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C385" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D385" t="b">
-        <v>1</v>
-      </c>
-      <c r="E385" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F385" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>8</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D386" t="b">
-        <v>1</v>
-      </c>
-      <c r="E386" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F386" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>8</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D387" t="b">
-        <v>1</v>
-      </c>
-      <c r="E387" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F387" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>8</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C388" s="3" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D388" t="b">
-        <v>1</v>
-      </c>
-      <c r="E388" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F388" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>8</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C389" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D389" t="b">
-        <v>1</v>
-      </c>
-      <c r="E389" s="3" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F389" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>8</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C390" s="3" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D390" t="b">
-        <v>1</v>
-      </c>
-      <c r="E390" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F390" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H390" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H250" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="11" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C191">
+  <conditionalFormatting sqref="C97">
     <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C192">
+  <conditionalFormatting sqref="C98">
     <cfRule type="duplicateValues" dxfId="9" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C193">
+  <conditionalFormatting sqref="C99">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C350:C355 C358:C377 C380:C381">
+  <conditionalFormatting sqref="C210:C215 C218:C237 C240:C241">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C388">
+  <conditionalFormatting sqref="C248">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C389">
+  <conditionalFormatting sqref="C249">
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C390">
+  <conditionalFormatting sqref="C250">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E380:E381">
+  <conditionalFormatting sqref="E240:E241">
     <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E388">
+  <conditionalFormatting sqref="E248">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E389">
+  <conditionalFormatting sqref="E249">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E390">
+  <conditionalFormatting sqref="E250">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inst/resources/dependency_schema_data_household_template.xlsx
+++ b/inst/resources/dependency_schema_data_household_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C32BFF-039D-4127-A18E-B600D7F5AE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117BE7C2-297A-469D-BB59-76FF72B535A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="2325" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -247,9 +247,6 @@
     <t>fsl_fcs_meat</t>
   </si>
   <si>
-    <t>fsl_fcs_meat &lt; 5</t>
-  </si>
-  <si>
     <t>flag_sd_foodgroup</t>
   </si>
   <si>
@@ -580,12 +577,6 @@
     <t>fsl_lcsi_crisis_yes,fsl_lcsi_crisis_exhaust,fsl_lcsi_stress_yes,fsl_lcsi_stress_exhaust,fsl_lcsi_emergency_yes,fsl_lcsi_emergency_exhaust</t>
   </si>
   <si>
-    <t>fsl_lcsi_emergency_yes == 1 | fsl_lcsi_emergency_exhaust == 1</t>
-  </si>
-  <si>
-    <t>fsl_lcsi_stress_yes == 1 | fsl_lcsi_stress_exhaust == 1 | fsl_lcsi_crisis_yes == 1 | fsl_lcsi_crisis_exhaust == 1</t>
-  </si>
-  <si>
     <t>flag_lcsi_severity</t>
   </si>
   <si>
@@ -2297,6 +2288,15 @@
   </si>
   <si>
     <t>lcsi_count_na</t>
+  </si>
+  <si>
+    <t>fsl_fcs_meat &lt; 5 &amp; fsl_fcs_dairy &lt; 5</t>
+  </si>
+  <si>
+    <t>fsl_lcsi_stress_yes == 1 | fsl_lcsi_stress_exhaust == 1</t>
+  </si>
+  <si>
+    <t>fsl_lcsi_emergency_yes == 1 | fsl_lcsi_emergency_exhaust == 1 | fsl_lcsi_crisis_yes == 1 | fsl_lcsi_crisis_exhaust == 1</t>
   </si>
 </sst>
 </file>
@@ -2315,6 +2315,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3247,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>755</v>
       </c>
       <c r="F22" t="s">
         <v>48</v>
@@ -3258,16 +3259,16 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>76</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>77</v>
-      </c>
-      <c r="E23" t="s">
-        <v>78</v>
       </c>
       <c r="F23" t="s">
         <v>48</v>
@@ -3278,16 +3279,16 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
         <v>79</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
         <v>80</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>81</v>
       </c>
       <c r="F24" t="s">
         <v>48</v>
@@ -3298,16 +3299,16 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>83</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>84</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -3318,16 +3319,16 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
         <v>85</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>86</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>87</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3338,16 +3339,16 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
         <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>89</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3358,16 +3359,16 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>91</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3378,16 +3379,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
         <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>93</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3398,16 +3399,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>94</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>95</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3418,16 +3419,16 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>98</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3438,16 +3439,16 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
         <v>99</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>100</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>101</v>
-      </c>
-      <c r="E32" t="s">
-        <v>102</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3458,16 +3459,16 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
         <v>103</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>104</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>105</v>
-      </c>
-      <c r="E33" t="s">
-        <v>106</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3478,16 +3479,16 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s">
         <v>107</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>108</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>109</v>
-      </c>
-      <c r="E34" t="s">
-        <v>110</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3498,16 +3499,16 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
         <v>111</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>112</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>113</v>
-      </c>
-      <c r="E35" t="s">
-        <v>114</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3518,16 +3519,16 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s">
         <v>115</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>116</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>117</v>
-      </c>
-      <c r="E36" t="s">
-        <v>118</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3538,16 +3539,16 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
         <v>119</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>120</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>122</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -3558,16 +3559,16 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" t="s">
         <v>123</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>124</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>125</v>
-      </c>
-      <c r="E38" t="s">
-        <v>126</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -3578,16 +3579,16 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
         <v>127</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>128</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>129</v>
-      </c>
-      <c r="E39" t="s">
-        <v>130</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
@@ -3598,16 +3599,16 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" t="s">
         <v>131</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>132</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>134</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
@@ -3618,16 +3619,16 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" t="s">
         <v>135</v>
       </c>
-      <c r="C41" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>136</v>
-      </c>
-      <c r="E41" t="s">
-        <v>137</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
@@ -3638,16 +3639,16 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
         <v>138</v>
       </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>139</v>
-      </c>
-      <c r="E42" t="s">
-        <v>140</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
@@ -3658,16 +3659,16 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" t="s">
         <v>141</v>
       </c>
-      <c r="C43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>142</v>
-      </c>
-      <c r="E43" t="s">
-        <v>143</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
@@ -3678,16 +3679,16 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" t="s">
         <v>144</v>
       </c>
-      <c r="C44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>145</v>
-      </c>
-      <c r="E44" t="s">
-        <v>146</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -3698,16 +3699,16 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" t="s">
         <v>147</v>
       </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>148</v>
-      </c>
-      <c r="E45" t="s">
-        <v>149</v>
       </c>
       <c r="F45" t="s">
         <v>13</v>
@@ -3718,16 +3719,16 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" t="s">
         <v>150</v>
       </c>
-      <c r="C46" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>151</v>
-      </c>
-      <c r="E46" t="s">
-        <v>152</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
@@ -3738,16 +3739,16 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" t="s">
         <v>153</v>
       </c>
-      <c r="C47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>154</v>
-      </c>
-      <c r="E47" t="s">
-        <v>155</v>
       </c>
       <c r="F47" t="s">
         <v>13</v>
@@ -3758,16 +3759,16 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" t="s">
         <v>156</v>
       </c>
-      <c r="C48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>157</v>
-      </c>
-      <c r="E48" t="s">
-        <v>158</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
@@ -3778,16 +3779,16 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" t="s">
         <v>159</v>
       </c>
-      <c r="C49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>160</v>
-      </c>
-      <c r="E49" t="s">
-        <v>161</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
@@ -3798,16 +3799,16 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" t="s">
         <v>162</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>163</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>164</v>
-      </c>
-      <c r="E50" t="s">
-        <v>165</v>
       </c>
       <c r="F50" t="s">
         <v>48</v>
@@ -3818,16 +3819,16 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" t="s">
         <v>166</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
         <v>167</v>
-      </c>
-      <c r="D51" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>168</v>
       </c>
       <c r="F51" t="s">
         <v>48</v>
@@ -3838,16 +3839,16 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
         <v>169</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>170</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>171</v>
-      </c>
-      <c r="E52" t="s">
-        <v>172</v>
       </c>
       <c r="F52" t="s">
         <v>48</v>
@@ -3858,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s">
         <v>173</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
         <v>174</v>
-      </c>
-      <c r="D53" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>175</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -3878,16 +3879,16 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s">
         <v>176</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>177</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>178</v>
-      </c>
-      <c r="E54" t="s">
-        <v>179</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -3898,16 +3899,16 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" t="s">
         <v>180</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
         <v>181</v>
-      </c>
-      <c r="D55" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>182</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -3918,16 +3919,16 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" t="s">
         <v>183</v>
       </c>
-      <c r="C56" t="s">
-        <v>184</v>
-      </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>757</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>756</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -3938,16 +3939,16 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C57" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -3958,16 +3959,16 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
@@ -3978,16 +3979,16 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -3998,16 +3999,16 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" t="s">
+        <v>193</v>
+      </c>
+      <c r="D60" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60" t="s">
         <v>195</v>
-      </c>
-      <c r="C60" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" t="s">
-        <v>197</v>
-      </c>
-      <c r="E60" t="s">
-        <v>198</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -4018,16 +4019,16 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D61" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E61" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
@@ -4038,16 +4039,16 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
@@ -4058,16 +4059,16 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -4078,16 +4079,16 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -4098,7 +4099,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C65" t="s">
         <v>73</v>
@@ -4107,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -4118,16 +4119,16 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -4138,16 +4139,16 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D67" t="b">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
@@ -4158,16 +4159,16 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
@@ -4178,16 +4179,16 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C69" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D69" t="b">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -4198,16 +4199,16 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D70" t="b">
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F70" t="s">
         <v>13</v>
@@ -4218,16 +4219,16 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
@@ -4238,16 +4239,16 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C72" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -4258,16 +4259,16 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D73" t="b">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
@@ -4278,16 +4279,16 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C74" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -4298,16 +4299,16 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C75" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D75" t="b">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
@@ -4318,16 +4319,16 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C76" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E76" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -4338,16 +4339,16 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" t="s">
+        <v>243</v>
+      </c>
+      <c r="D77" t="s">
+        <v>244</v>
+      </c>
+      <c r="E77" t="s">
         <v>245</v>
-      </c>
-      <c r="C77" t="s">
-        <v>246</v>
-      </c>
-      <c r="D77" t="s">
-        <v>247</v>
-      </c>
-      <c r="E77" t="s">
-        <v>248</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
@@ -4358,16 +4359,16 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D78" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E78" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -4378,16 +4379,16 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D79" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E79" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -4398,16 +4399,16 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
@@ -4418,16 +4419,16 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D81" t="b">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -4438,16 +4439,16 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D82" t="b">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
@@ -4458,16 +4459,16 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
+        <v>258</v>
+      </c>
+      <c r="C83" t="s">
+        <v>259</v>
+      </c>
+      <c r="D83" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" t="s">
         <v>261</v>
-      </c>
-      <c r="C83" t="s">
-        <v>262</v>
-      </c>
-      <c r="D83" t="s">
-        <v>263</v>
-      </c>
-      <c r="E83" t="s">
-        <v>264</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -4478,16 +4479,16 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D84" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E84" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -4498,16 +4499,16 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D85" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E85" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F85" t="s">
         <v>13</v>
@@ -4518,16 +4519,16 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F86" t="s">
         <v>13</v>
@@ -4538,16 +4539,16 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C87" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D87" t="b">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
@@ -4558,16 +4559,16 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C88" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
         <v>272</v>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" t="s">
-        <v>275</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
@@ -4578,16 +4579,16 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C89" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D89" t="b">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
@@ -4598,16 +4599,16 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
@@ -4618,16 +4619,16 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C91" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D91" t="b">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
@@ -4638,16 +4639,16 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
+        <v>281</v>
+      </c>
+      <c r="C92" t="s">
+        <v>282</v>
+      </c>
+      <c r="D92" t="s">
+        <v>283</v>
+      </c>
+      <c r="E92" t="s">
         <v>284</v>
-      </c>
-      <c r="C92" t="s">
-        <v>285</v>
-      </c>
-      <c r="D92" t="s">
-        <v>286</v>
-      </c>
-      <c r="E92" t="s">
-        <v>287</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
@@ -4658,16 +4659,16 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
+        <v>285</v>
+      </c>
+      <c r="C93" t="s">
+        <v>286</v>
+      </c>
+      <c r="D93" t="s">
+        <v>287</v>
+      </c>
+      <c r="E93" t="s">
         <v>288</v>
-      </c>
-      <c r="C93" t="s">
-        <v>289</v>
-      </c>
-      <c r="D93" t="s">
-        <v>290</v>
-      </c>
-      <c r="E93" t="s">
-        <v>291</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
@@ -4678,16 +4679,16 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
+        <v>289</v>
+      </c>
+      <c r="C94" t="s">
+        <v>290</v>
+      </c>
+      <c r="D94" t="s">
+        <v>291</v>
+      </c>
+      <c r="E94" t="s">
         <v>292</v>
-      </c>
-      <c r="C94" t="s">
-        <v>293</v>
-      </c>
-      <c r="D94" t="s">
-        <v>294</v>
-      </c>
-      <c r="E94" t="s">
-        <v>295</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
@@ -4698,16 +4699,16 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
+        <v>293</v>
+      </c>
+      <c r="C95" t="s">
+        <v>294</v>
+      </c>
+      <c r="D95" t="s">
+        <v>295</v>
+      </c>
+      <c r="E95" t="s">
         <v>296</v>
-      </c>
-      <c r="C95" t="s">
-        <v>297</v>
-      </c>
-      <c r="D95" t="s">
-        <v>298</v>
-      </c>
-      <c r="E95" t="s">
-        <v>299</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
@@ -4718,16 +4719,16 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C96" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D96" t="s">
+        <v>296</v>
+      </c>
+      <c r="E96" t="s">
         <v>299</v>
-      </c>
-      <c r="E96" t="s">
-        <v>302</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
@@ -4738,16 +4739,16 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
+        <v>300</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D97" t="s">
+        <v>302</v>
+      </c>
+      <c r="E97" t="s">
         <v>303</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D97" t="s">
-        <v>305</v>
-      </c>
-      <c r="E97" t="s">
-        <v>306</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
@@ -4758,16 +4759,16 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F98" t="s">
         <v>13</v>
@@ -4778,16 +4779,16 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D99" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E99" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
@@ -4798,16 +4799,16 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
+        <v>309</v>
+      </c>
+      <c r="C100" t="s">
+        <v>310</v>
+      </c>
+      <c r="D100" t="s">
+        <v>311</v>
+      </c>
+      <c r="E100" t="s">
         <v>312</v>
-      </c>
-      <c r="C100" t="s">
-        <v>313</v>
-      </c>
-      <c r="D100" t="s">
-        <v>314</v>
-      </c>
-      <c r="E100" t="s">
-        <v>315</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -4818,16 +4819,16 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C101" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D101" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E101" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
@@ -4838,16 +4839,16 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C102" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D102" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E102" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
@@ -4858,16 +4859,16 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C103" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D103" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E103" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
@@ -4878,16 +4879,16 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C104" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D104" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E104" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
@@ -4898,16 +4899,16 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C105" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D105" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E105" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
@@ -4918,16 +4919,16 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C106" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D106" t="s">
+        <v>324</v>
+      </c>
+      <c r="E106" t="s">
         <v>327</v>
-      </c>
-      <c r="E106" t="s">
-        <v>330</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
@@ -4938,16 +4939,16 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C107" t="s">
+        <v>326</v>
+      </c>
+      <c r="D107" t="s">
+        <v>324</v>
+      </c>
+      <c r="E107" t="s">
         <v>329</v>
-      </c>
-      <c r="D107" t="s">
-        <v>327</v>
-      </c>
-      <c r="E107" t="s">
-        <v>332</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
@@ -4958,16 +4959,16 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C108" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D108" t="b">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
@@ -4978,16 +4979,16 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C109" t="s">
+        <v>331</v>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" t="s">
         <v>334</v>
-      </c>
-      <c r="D109" t="b">
-        <v>1</v>
-      </c>
-      <c r="E109" t="s">
-        <v>337</v>
       </c>
       <c r="F109" t="s">
         <v>13</v>
@@ -4998,16 +4999,16 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
+        <v>335</v>
+      </c>
+      <c r="C110" t="s">
+        <v>336</v>
+      </c>
+      <c r="D110" t="s">
+        <v>337</v>
+      </c>
+      <c r="E110" t="s">
         <v>338</v>
-      </c>
-      <c r="C110" t="s">
-        <v>339</v>
-      </c>
-      <c r="D110" t="s">
-        <v>340</v>
-      </c>
-      <c r="E110" t="s">
-        <v>341</v>
       </c>
       <c r="F110" t="s">
         <v>47</v>
@@ -5018,16 +5019,16 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C111" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D111" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E111" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F111" t="s">
         <v>47</v>
@@ -5038,16 +5039,16 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D112" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E112" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F112" t="s">
         <v>47</v>
@@ -5058,16 +5059,16 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
+        <v>345</v>
+      </c>
+      <c r="C113" t="s">
+        <v>346</v>
+      </c>
+      <c r="D113" t="s">
+        <v>347</v>
+      </c>
+      <c r="E113" t="s">
         <v>348</v>
-      </c>
-      <c r="C113" t="s">
-        <v>349</v>
-      </c>
-      <c r="D113" t="s">
-        <v>350</v>
-      </c>
-      <c r="E113" t="s">
-        <v>351</v>
       </c>
       <c r="F113" t="s">
         <v>13</v>
@@ -5078,16 +5079,16 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
+        <v>349</v>
+      </c>
+      <c r="C114" t="s">
+        <v>350</v>
+      </c>
+      <c r="D114" t="s">
+        <v>351</v>
+      </c>
+      <c r="E114" t="s">
         <v>352</v>
-      </c>
-      <c r="C114" t="s">
-        <v>353</v>
-      </c>
-      <c r="D114" t="s">
-        <v>354</v>
-      </c>
-      <c r="E114" t="s">
-        <v>355</v>
       </c>
       <c r="F114" t="s">
         <v>13</v>
@@ -5098,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C115" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D115" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E115" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F115" t="s">
         <v>13</v>
@@ -5118,16 +5119,16 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C116" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D116" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E116" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F116" t="s">
         <v>13</v>
@@ -5138,16 +5139,16 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C117" t="s">
+        <v>357</v>
+      </c>
+      <c r="D117" t="s">
+        <v>358</v>
+      </c>
+      <c r="E117" t="s">
         <v>360</v>
-      </c>
-      <c r="D117" t="s">
-        <v>361</v>
-      </c>
-      <c r="E117" t="s">
-        <v>363</v>
       </c>
       <c r="F117" t="s">
         <v>13</v>
@@ -5158,16 +5159,16 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
+        <v>361</v>
+      </c>
+      <c r="C118" t="s">
+        <v>362</v>
+      </c>
+      <c r="D118" t="s">
+        <v>363</v>
+      </c>
+      <c r="E118" t="s">
         <v>364</v>
-      </c>
-      <c r="C118" t="s">
-        <v>365</v>
-      </c>
-      <c r="D118" t="s">
-        <v>366</v>
-      </c>
-      <c r="E118" t="s">
-        <v>367</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
@@ -5178,16 +5179,16 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C119" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E119" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F119" t="s">
         <v>13</v>
@@ -5198,16 +5199,16 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C120" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E120" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -5218,16 +5219,16 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C121" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E121" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F121" t="s">
         <v>13</v>
@@ -5238,16 +5239,16 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C122" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E122" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
@@ -5258,16 +5259,16 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C123" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D123" t="b">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F123" t="s">
         <v>13</v>
@@ -5278,16 +5279,16 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C124" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D124" t="b">
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -5298,16 +5299,16 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C125" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D125" t="b">
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F125" t="s">
         <v>13</v>
@@ -5318,16 +5319,16 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
+        <v>386</v>
+      </c>
+      <c r="C126" t="s">
+        <v>387</v>
+      </c>
+      <c r="D126" t="s">
+        <v>388</v>
+      </c>
+      <c r="E126" t="s">
         <v>389</v>
-      </c>
-      <c r="C126" t="s">
-        <v>390</v>
-      </c>
-      <c r="D126" t="s">
-        <v>391</v>
-      </c>
-      <c r="E126" t="s">
-        <v>392</v>
       </c>
       <c r="F126" t="s">
         <v>13</v>
@@ -5338,16 +5339,16 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
+        <v>390</v>
+      </c>
+      <c r="C127" t="s">
+        <v>391</v>
+      </c>
+      <c r="D127" t="s">
+        <v>392</v>
+      </c>
+      <c r="E127" t="s">
         <v>393</v>
-      </c>
-      <c r="C127" t="s">
-        <v>394</v>
-      </c>
-      <c r="D127" t="s">
-        <v>395</v>
-      </c>
-      <c r="E127" t="s">
-        <v>396</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
@@ -5358,16 +5359,16 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C128" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D128" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E128" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F128" t="s">
         <v>13</v>
@@ -5378,16 +5379,16 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C129" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D129" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E129" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F129" t="s">
         <v>13</v>
@@ -5398,16 +5399,16 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
+        <v>398</v>
+      </c>
+      <c r="C130" t="s">
+        <v>399</v>
+      </c>
+      <c r="D130" t="s">
+        <v>400</v>
+      </c>
+      <c r="E130" t="s">
         <v>401</v>
-      </c>
-      <c r="C130" t="s">
-        <v>402</v>
-      </c>
-      <c r="D130" t="s">
-        <v>403</v>
-      </c>
-      <c r="E130" t="s">
-        <v>404</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
@@ -5418,16 +5419,16 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
+        <v>402</v>
+      </c>
+      <c r="C131" t="s">
+        <v>403</v>
+      </c>
+      <c r="D131" t="s">
+        <v>404</v>
+      </c>
+      <c r="E131" t="s">
         <v>405</v>
-      </c>
-      <c r="C131" t="s">
-        <v>406</v>
-      </c>
-      <c r="D131" t="s">
-        <v>407</v>
-      </c>
-      <c r="E131" t="s">
-        <v>408</v>
       </c>
       <c r="F131" t="s">
         <v>13</v>
@@ -5438,16 +5439,16 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
+        <v>406</v>
+      </c>
+      <c r="C132" t="s">
+        <v>407</v>
+      </c>
+      <c r="D132" t="s">
+        <v>408</v>
+      </c>
+      <c r="E132" t="s">
         <v>409</v>
-      </c>
-      <c r="C132" t="s">
-        <v>410</v>
-      </c>
-      <c r="D132" t="s">
-        <v>411</v>
-      </c>
-      <c r="E132" t="s">
-        <v>412</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -5458,16 +5459,16 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
+        <v>410</v>
+      </c>
+      <c r="C133" t="s">
+        <v>411</v>
+      </c>
+      <c r="D133" t="s">
+        <v>412</v>
+      </c>
+      <c r="E133" t="s">
         <v>413</v>
-      </c>
-      <c r="C133" t="s">
-        <v>414</v>
-      </c>
-      <c r="D133" t="s">
-        <v>415</v>
-      </c>
-      <c r="E133" t="s">
-        <v>416</v>
       </c>
       <c r="F133" t="s">
         <v>13</v>
@@ -5478,16 +5479,16 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
+        <v>414</v>
+      </c>
+      <c r="C134" t="s">
+        <v>415</v>
+      </c>
+      <c r="D134" t="s">
+        <v>416</v>
+      </c>
+      <c r="E134" t="s">
         <v>417</v>
-      </c>
-      <c r="C134" t="s">
-        <v>418</v>
-      </c>
-      <c r="D134" t="s">
-        <v>419</v>
-      </c>
-      <c r="E134" t="s">
-        <v>420</v>
       </c>
       <c r="F134" t="s">
         <v>13</v>
@@ -5498,16 +5499,16 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C135" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D135" t="b">
         <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F135" t="s">
         <v>47</v>
@@ -5518,16 +5519,16 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C136" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D136" t="b">
         <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F136" t="s">
         <v>47</v>
@@ -5538,16 +5539,16 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C137" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D137" t="b">
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F137" t="s">
         <v>47</v>
@@ -5558,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C138" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D138" t="b">
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F138" t="s">
         <v>47</v>
@@ -5578,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D139" t="b">
         <v>1</v>
       </c>
       <c r="E139" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F139" t="s">
         <v>47</v>
@@ -5598,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C140" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D140" t="b">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F140" t="s">
         <v>47</v>
@@ -5618,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C141" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D141" t="b">
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F141" t="s">
         <v>47</v>
@@ -5638,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C142" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D142" t="b">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F142" t="s">
         <v>13</v>
@@ -5658,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C143" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D143" t="b">
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F143" t="s">
         <v>13</v>
@@ -5678,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C144" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D144" t="b">
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F144" t="s">
         <v>13</v>
@@ -5698,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C145" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D145" t="b">
         <v>1</v>
       </c>
       <c r="E145" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F145" t="s">
         <v>13</v>
@@ -5718,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C146" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D146" t="b">
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F146" t="s">
         <v>13</v>
@@ -5738,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C147" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D147" t="b">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F147" t="s">
         <v>13</v>
@@ -5758,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C148" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D148" t="b">
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F148" t="s">
         <v>13</v>
@@ -5778,16 +5779,16 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C149" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D149" t="b">
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F149" t="s">
         <v>13</v>
@@ -5798,16 +5799,16 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C150" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D150" t="b">
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F150" t="s">
         <v>13</v>
@@ -5818,16 +5819,16 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C151" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D151" t="b">
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F151" t="s">
         <v>13</v>
@@ -5838,16 +5839,16 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C152" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D152" t="b">
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F152" t="s">
         <v>13</v>
@@ -5858,16 +5859,16 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C153" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D153" t="b">
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F153" t="s">
         <v>13</v>
@@ -5878,16 +5879,16 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C154" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D154" t="b">
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F154" t="s">
         <v>13</v>
@@ -5898,16 +5899,16 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C155" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D155" t="b">
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F155" t="s">
         <v>13</v>
@@ -5918,16 +5919,16 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C156" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D156" t="b">
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F156" t="s">
         <v>13</v>
@@ -5938,16 +5939,16 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C157" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D157" t="b">
         <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F157" t="s">
         <v>13</v>
@@ -5958,16 +5959,16 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C158" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D158" t="b">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F158" t="s">
         <v>13</v>
@@ -5978,16 +5979,16 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C159" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F159" t="s">
         <v>13</v>
@@ -5998,16 +5999,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C160" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D160" t="b">
         <v>1</v>
       </c>
       <c r="E160" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F160" t="s">
         <v>13</v>
@@ -6018,16 +6019,16 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C161" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D161" t="b">
         <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F161" t="s">
         <v>13</v>
@@ -6038,16 +6039,16 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C162" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D162" t="b">
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F162" t="s">
         <v>13</v>
@@ -6058,16 +6059,16 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C163" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D163" t="b">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F163" t="s">
         <v>13</v>
@@ -6078,16 +6079,16 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C164" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D164" t="b">
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F164" t="s">
         <v>13</v>
@@ -6098,16 +6099,16 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C165" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D165" t="b">
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F165" t="s">
         <v>13</v>
@@ -6118,16 +6119,16 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C166" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D166" t="b">
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F166" t="s">
         <v>13</v>
@@ -6138,16 +6139,16 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C167" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D167" t="b">
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F167" t="s">
         <v>13</v>
@@ -6158,16 +6159,16 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C168" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D168" t="b">
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F168" t="s">
         <v>13</v>
@@ -6178,16 +6179,16 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C169" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D169" t="b">
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F169" t="s">
         <v>13</v>
@@ -6198,16 +6199,16 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C170" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F170" t="s">
         <v>13</v>
@@ -6218,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C171" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D171" t="b">
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F171" t="s">
         <v>13</v>
@@ -6238,16 +6239,16 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C172" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D172" t="b">
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F172" t="s">
         <v>13</v>
@@ -6258,16 +6259,16 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C173" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D173" t="b">
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -6278,16 +6279,16 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C174" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D174" t="b">
         <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F174" t="s">
         <v>13</v>
@@ -6298,16 +6299,16 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C175" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D175" t="b">
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
@@ -6318,16 +6319,16 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C176" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D176" t="b">
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F176" t="s">
         <v>13</v>
@@ -6338,16 +6339,16 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C177" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D177" t="b">
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F177" t="s">
         <v>13</v>
@@ -6358,16 +6359,16 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C178" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D178" t="b">
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F178" t="s">
         <v>13</v>
@@ -6378,16 +6379,16 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C179" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D179" t="b">
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F179" t="s">
         <v>13</v>
@@ -6398,16 +6399,16 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C180" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D180" t="b">
         <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F180" t="s">
         <v>13</v>
@@ -6418,16 +6419,16 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C181" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D181" t="b">
         <v>1</v>
       </c>
       <c r="E181" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F181" t="s">
         <v>13</v>
@@ -6438,16 +6439,16 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C182" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D182" t="b">
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F182" t="s">
         <v>13</v>
@@ -6458,16 +6459,16 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C183" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D183" t="b">
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F183" t="s">
         <v>13</v>
@@ -6478,16 +6479,16 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C184" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D184" t="b">
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F184" t="s">
         <v>13</v>
@@ -6498,16 +6499,16 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C185" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D185" t="b">
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F185" t="s">
         <v>13</v>
@@ -6518,16 +6519,16 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C186" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D186" t="b">
         <v>1</v>
       </c>
       <c r="E186" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F186" t="s">
         <v>13</v>
@@ -6538,16 +6539,16 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C187" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D187" t="b">
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F187" t="s">
         <v>13</v>
@@ -6558,16 +6559,16 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C188" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D188" t="b">
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
@@ -6578,16 +6579,16 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C189" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D189" t="b">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F189" t="s">
         <v>13</v>
@@ -6598,16 +6599,16 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C190" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D190" t="b">
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -6618,16 +6619,16 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C191" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D191" t="b">
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F191" t="s">
         <v>13</v>
@@ -6638,16 +6639,16 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C192" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D192" t="b">
         <v>1</v>
       </c>
       <c r="E192" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F192" t="s">
         <v>13</v>
@@ -6658,16 +6659,16 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C193" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D193" t="b">
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F193" t="s">
         <v>13</v>
@@ -6678,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C194" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D194" t="b">
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="F194" t="s">
         <v>13</v>
@@ -6698,16 +6699,16 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C195" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D195" t="b">
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -6718,16 +6719,16 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C196" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D196" t="b">
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F196" t="s">
         <v>13</v>
@@ -6738,16 +6739,16 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C197" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D197" t="b">
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F197" t="s">
         <v>13</v>
@@ -6758,16 +6759,16 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C198" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D198" t="b">
         <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -6778,16 +6779,16 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C199" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D199" t="b">
         <v>1</v>
       </c>
       <c r="E199" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F199" t="s">
         <v>13</v>
@@ -6798,16 +6799,16 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C200" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D200" t="b">
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="F200" t="s">
         <v>13</v>
@@ -6818,16 +6819,16 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="b">
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F201" t="s">
         <v>13</v>
@@ -6838,16 +6839,16 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C202" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D202" t="b">
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F202" t="s">
         <v>13</v>
@@ -6858,16 +6859,16 @@
         <v>8</v>
       </c>
       <c r="B203" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C203" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D203" t="b">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F203" t="s">
         <v>13</v>
@@ -6878,16 +6879,16 @@
         <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C204" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D204" t="b">
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -6898,16 +6899,16 @@
         <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C205" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D205" t="b">
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F205" t="s">
         <v>13</v>
@@ -6918,16 +6919,16 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D206" t="b">
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -6938,16 +6939,16 @@
         <v>8</v>
       </c>
       <c r="B207" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C207" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D207" t="b">
         <v>1</v>
       </c>
       <c r="E207" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F207" t="s">
         <v>13</v>
@@ -6958,16 +6959,16 @@
         <v>8</v>
       </c>
       <c r="B208" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C208" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D208" t="b">
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F208" t="s">
         <v>13</v>
@@ -6978,16 +6979,16 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C209" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D209" t="b">
         <v>1</v>
       </c>
       <c r="E209" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F209" t="s">
         <v>13</v>
@@ -6998,16 +6999,16 @@
         <v>8</v>
       </c>
       <c r="B210" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C210" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D210" t="b">
         <v>1</v>
       </c>
       <c r="E210" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F210" t="s">
         <v>13</v>
@@ -7018,16 +7019,16 @@
         <v>8</v>
       </c>
       <c r="B211" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C211" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D211" t="b">
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F211" t="s">
         <v>13</v>
@@ -7038,16 +7039,16 @@
         <v>8</v>
       </c>
       <c r="B212" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C212" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D212" t="b">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -7058,16 +7059,16 @@
         <v>8</v>
       </c>
       <c r="B213" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C213" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D213" t="b">
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F213" t="s">
         <v>13</v>
@@ -7078,16 +7079,16 @@
         <v>8</v>
       </c>
       <c r="B214" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C214" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D214" t="b">
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F214" t="s">
         <v>13</v>
@@ -7098,16 +7099,16 @@
         <v>8</v>
       </c>
       <c r="B215" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C215" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D215" t="b">
         <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F215" t="s">
         <v>13</v>
@@ -7118,16 +7119,16 @@
         <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C216" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D216" t="b">
         <v>1</v>
       </c>
       <c r="E216" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F216" t="s">
         <v>13</v>
@@ -7138,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="B217" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C217" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D217" t="b">
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F217" t="s">
         <v>13</v>
@@ -7158,16 +7159,16 @@
         <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C218" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D218" t="b">
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="F218" t="s">
         <v>13</v>
@@ -7178,16 +7179,16 @@
         <v>8</v>
       </c>
       <c r="B219" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C219" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D219" t="b">
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F219" t="s">
         <v>13</v>
@@ -7198,16 +7199,16 @@
         <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C220" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D220" t="b">
         <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F220" t="s">
         <v>13</v>
@@ -7218,16 +7219,16 @@
         <v>8</v>
       </c>
       <c r="B221" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C221" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D221" t="b">
         <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F221" t="s">
         <v>13</v>
@@ -7238,16 +7239,16 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C222" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D222" t="b">
         <v>1</v>
       </c>
       <c r="E222" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F222" t="s">
         <v>13</v>
@@ -7258,16 +7259,16 @@
         <v>8</v>
       </c>
       <c r="B223" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C223" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D223" t="b">
         <v>1</v>
       </c>
       <c r="E223" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F223" t="s">
         <v>13</v>
@@ -7278,16 +7279,16 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C224" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D224" t="b">
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F224" t="s">
         <v>13</v>
@@ -7298,16 +7299,16 @@
         <v>8</v>
       </c>
       <c r="B225" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C225" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D225" t="b">
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F225" t="s">
         <v>13</v>
@@ -7318,16 +7319,16 @@
         <v>8</v>
       </c>
       <c r="B226" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C226" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D226" t="b">
         <v>1</v>
       </c>
       <c r="E226" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F226" t="s">
         <v>13</v>
@@ -7338,16 +7339,16 @@
         <v>8</v>
       </c>
       <c r="B227" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C227" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D227" t="b">
         <v>1</v>
       </c>
       <c r="E227" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F227" t="s">
         <v>13</v>
@@ -7358,16 +7359,16 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C228" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D228" t="b">
         <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F228" t="s">
         <v>13</v>
@@ -7378,16 +7379,16 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C229" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
       </c>
       <c r="E229" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F229" t="s">
         <v>13</v>
@@ -7398,16 +7399,16 @@
         <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C230" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D230" t="b">
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="F230" t="s">
         <v>13</v>
@@ -7418,16 +7419,16 @@
         <v>8</v>
       </c>
       <c r="B231" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C231" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D231" t="b">
         <v>1</v>
       </c>
       <c r="E231" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="F231" t="s">
         <v>13</v>
@@ -7438,16 +7439,16 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C232" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="F232" t="s">
         <v>13</v>
@@ -7458,16 +7459,16 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C233" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D233" t="b">
         <v>1</v>
       </c>
       <c r="E233" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -7478,16 +7479,16 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C234" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -7498,16 +7499,16 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C235" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D235" t="b">
         <v>1</v>
       </c>
       <c r="E235" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F235" t="s">
         <v>13</v>
@@ -7518,16 +7519,16 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C236" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F236" t="s">
         <v>13</v>
@@ -7538,16 +7539,16 @@
         <v>8</v>
       </c>
       <c r="B237" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C237" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D237" t="b">
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -7558,16 +7559,16 @@
         <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C238" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D238" t="b">
         <v>1</v>
       </c>
       <c r="E238" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F238" t="s">
         <v>13</v>
@@ -7578,16 +7579,16 @@
         <v>8</v>
       </c>
       <c r="B239" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C239" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D239" t="b">
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F239" t="s">
         <v>13</v>
@@ -7598,16 +7599,16 @@
         <v>8</v>
       </c>
       <c r="B240" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C240" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D240" t="b">
         <v>1</v>
       </c>
       <c r="E240" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -7618,16 +7619,16 @@
         <v>8</v>
       </c>
       <c r="B241" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C241" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D241" t="b">
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F241" t="s">
         <v>13</v>
@@ -7638,16 +7639,16 @@
         <v>8</v>
       </c>
       <c r="B242" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C242" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D242" t="b">
         <v>1</v>
       </c>
       <c r="E242" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F242" t="s">
         <v>13</v>
@@ -7658,16 +7659,16 @@
         <v>8</v>
       </c>
       <c r="B243" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C243" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D243" t="b">
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F243" t="s">
         <v>13</v>
@@ -7678,7 +7679,7 @@
         <v>8</v>
       </c>
       <c r="B244" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
@@ -7687,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F244" t="s">
         <v>13</v>
@@ -7698,16 +7699,16 @@
         <v>8</v>
       </c>
       <c r="B245" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C245" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D245" t="b">
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F245" t="s">
         <v>13</v>
@@ -7718,16 +7719,16 @@
         <v>8</v>
       </c>
       <c r="B246" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C246" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D246" t="b">
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F246" t="s">
         <v>13</v>
@@ -7738,16 +7739,16 @@
         <v>8</v>
       </c>
       <c r="B247" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C247" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D247" t="b">
         <v>1</v>
       </c>
       <c r="E247" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F247" t="s">
         <v>13</v>
@@ -7758,16 +7759,16 @@
         <v>8</v>
       </c>
       <c r="B248" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D248" t="b">
         <v>1</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F248" t="s">
         <v>13</v>
@@ -7778,16 +7779,16 @@
         <v>8</v>
       </c>
       <c r="B249" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D249" t="b">
         <v>1</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F249" t="s">
         <v>13</v>
@@ -7798,16 +7799,16 @@
         <v>8</v>
       </c>
       <c r="B250" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D250" t="b">
         <v>1</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F250" t="s">
         <v>13</v>
